--- a/output/bfm_summary/bfm_norep_pre/merging_points.xlsx
+++ b/output/bfm_summary/bfm_norep_pre/merging_points.xlsx
@@ -53,13 +53,14 @@
     <sheet name="CRI2022" sheetId="45" r:id="rId47"/>
     <sheet name="CRI2023" sheetId="46" r:id="rId48"/>
     <sheet name="BRA2024" sheetId="47" r:id="rId49"/>
+    <sheet name="CRI2024" sheetId="48" r:id="rId50"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="1377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="1377">
   <si>
     <t>p</t>
   </si>
@@ -4235,7 +4236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4263,22 +4264,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>0.80000001192092896</v>
+        <v>0.97000002861022949</v>
       </c>
       <c r="B2" s="1">
-        <v>-2.7755575615628914e-16</v>
+        <v>1.0091278553009033</v>
       </c>
       <c r="C2" s="1">
-        <v>54.600170135498047</v>
+        <v>0.91820687055587769</v>
       </c>
       <c r="D2" s="1">
-        <v>54.600170135498047</v>
+        <v>0.91820687055587769</v>
       </c>
       <c r="E2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="G2" s="1">
         <v>0.97000002861022949</v>
@@ -4286,1482 +4287,612 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>0.81000000238418579</v>
+        <v>0.98000001907348633</v>
       </c>
       <c r="B3" s="1">
-        <v>0.61939287185668945</v>
+        <v>1.0082000494003296</v>
       </c>
       <c r="C3" s="1">
-        <v>6.4394803047180176</v>
+        <v>0.72307229042053223</v>
       </c>
       <c r="D3" s="1">
-        <v>6.4394803047180176</v>
+        <v>0.75054579973220825</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>1740</v>
+        <v>37800</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>0.81999999284744263</v>
+        <v>0.99000000953674316</v>
       </c>
       <c r="B4" s="1">
-        <v>0.66477996110916138</v>
+        <v>1.0053199529647827</v>
       </c>
       <c r="C4" s="1">
-        <v>5.8184819221496582</v>
+        <v>0.95238149166107178</v>
       </c>
       <c r="D4" s="1">
-        <v>5.8184819221496582</v>
+        <v>0.75054579973220825</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>2400</v>
+        <v>60000</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>0.82999998331069946</v>
+        <v>0.99099999666213989</v>
       </c>
       <c r="B5" s="1">
-        <v>0.75146818161010742</v>
+        <v>1.0052666664123535</v>
       </c>
       <c r="C5" s="1">
-        <v>5.0434932708740234</v>
+        <v>0.62013190984725952</v>
       </c>
       <c r="D5" s="1">
-        <v>5.0434932708740234</v>
+        <v>0.70287430286407471</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>2580</v>
+        <v>61830</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>0.8399999737739563</v>
+        <v>0.99199998378753662</v>
       </c>
       <c r="B6" s="1">
-        <v>0.80351966619491577</v>
+        <v>1.0048784017562866</v>
       </c>
       <c r="C6" s="1">
-        <v>4.3730754852294922</v>
+        <v>0.31377652287483215</v>
       </c>
       <c r="D6" s="1">
-        <v>4.3730754852294922</v>
+        <v>0.70287430286407471</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>3192</v>
+        <v>68400</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>0.85000002384185791</v>
+        <v>0.99299997091293335</v>
       </c>
       <c r="B7" s="1">
-        <v>0.8204423189163208</v>
+        <v>1.0041824579238892</v>
       </c>
       <c r="C7" s="1">
-        <v>3.9393365383148193</v>
+        <v>0.89605492353439331</v>
       </c>
       <c r="D7" s="1">
-        <v>3.9393365383148193</v>
+        <v>0.70287430286407471</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>3600</v>
+        <v>72000</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>0.86000001430511475</v>
+        <v>0.99400001764297485</v>
       </c>
       <c r="B8" s="1">
-        <v>0.87987226247787476</v>
+        <v>1.0040736198425293</v>
       </c>
       <c r="C8" s="1">
-        <v>3.4673056602478027</v>
+        <v>0.49942862987518311</v>
       </c>
       <c r="D8" s="1">
-        <v>3.4673056602478027</v>
+        <v>0.55815458297729492</v>
       </c>
       <c r="E8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>4320</v>
+        <v>80400</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>0.87000000476837158</v>
+        <v>0.99500000476837158</v>
       </c>
       <c r="B9" s="1">
-        <v>0.88652157783508301</v>
+        <v>1.0035665035247803</v>
       </c>
       <c r="C9" s="1">
-        <v>3.1436817646026611</v>
+        <v>0.6035119891166687</v>
       </c>
       <c r="D9" s="1">
-        <v>3.1436817646026611</v>
+        <v>0.55815458297729492</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>4800</v>
+        <v>90000</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>0.87999999523162842</v>
+        <v>0.99599999189376831</v>
       </c>
       <c r="B10" s="1">
-        <v>0.93664610385894775</v>
+        <v>1.0031647682189941</v>
       </c>
       <c r="C10" s="1">
-        <v>2.8042750358581543</v>
+        <v>0.44894993305206299</v>
       </c>
       <c r="D10" s="1">
-        <v>2.8042750358581543</v>
+        <v>0.44894993305206299</v>
       </c>
       <c r="E10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>5898</v>
+        <v>105648</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>0.88999998569488525</v>
+        <v>0.99699997901916504</v>
       </c>
       <c r="B11" s="1">
-        <v>0.95268207788467407</v>
+        <v>1.0026088953018188</v>
       </c>
       <c r="C11" s="1">
-        <v>2.485933780670166</v>
+        <v>0.39892444014549255</v>
       </c>
       <c r="D11" s="1">
-        <v>2.485933780670166</v>
+        <v>0.39892444014549255</v>
       </c>
       <c r="E11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>6600</v>
+        <v>140400</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>0.89999997615814209</v>
+        <v>0.99800002574920654</v>
       </c>
       <c r="B12" s="1">
-        <v>0.97315526008605957</v>
+        <v>1.0020040273666382</v>
       </c>
       <c r="C12" s="1">
-        <v>2.1912167072296143</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>2.1912167072296143</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>7800</v>
+        <v>2772000</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>0.9100000262260437</v>
+        <v>0.99900001287460327</v>
       </c>
       <c r="B13" s="1">
-        <v>0.98778903484344482</v>
+        <v>1.0010010004043579</v>
       </c>
       <c r="C13" s="1">
-        <v>1.9221222400665283</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>1.9221222400665283</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>9120</v>
+        <v>2956800</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>0.92000001668930054</v>
+        <v>0.99910002946853638</v>
       </c>
       <c r="B14" s="1">
-        <v>0.99813425540924072</v>
+        <v>1.0009007453918457</v>
       </c>
       <c r="C14" s="1">
-        <v>1.6825003623962402</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>1.6825003623962402</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>10890</v>
+        <v>3141600</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>0.93000000715255737</v>
+        <v>0.99919998645782471</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0059856176376343</v>
+        <v>1.000800609588623</v>
       </c>
       <c r="C15" s="1">
-        <v>0.33065691590309143</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>0.99298334121704102</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>13160.615234375</v>
+        <v>3326400</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>0.93000000715255737</v>
+        <v>0.99930000305175781</v>
       </c>
       <c r="B16" s="1">
-        <v>1.0052965879440308</v>
+        <v>1.0007004737854004</v>
       </c>
       <c r="C16" s="1">
-        <v>0.36640837788581848</v>
-      </c>
-      <c r="D16" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>12900</v>
+        <v>3511200</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>0.93999999761581421</v>
+        <v>0.99940001964569092</v>
       </c>
       <c r="B17" s="1">
-        <v>0.99868446588516235</v>
+        <v>1.0006003379821777</v>
       </c>
       <c r="C17" s="1">
-        <v>1.1449018716812134</v>
-      </c>
-      <c r="D17" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>13560</v>
+        <v>3696000</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>0.93999999761581421</v>
+        <v>0.99949997663497925</v>
       </c>
       <c r="B18" s="1">
-        <v>0.99880129098892212</v>
+        <v>1.0005003213882446</v>
       </c>
       <c r="C18" s="1">
-        <v>1.1686465740203857</v>
+        <v>0</v>
       </c>
       <c r="D18" s="1">
-        <v>0.99298334121704102</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>13627.4697265625</v>
+        <v>3880800</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>0.94999998807907104</v>
+        <v>0.99959999322891235</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0002243518829346</v>
+        <v>1.000400185585022</v>
       </c>
       <c r="C19" s="1">
-        <v>1.3557202816009521</v>
-      </c>
-      <c r="D19" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>15870</v>
+        <v>4065600</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>0.94999998807907104</v>
+        <v>0.99970000982284546</v>
       </c>
       <c r="B20" s="1">
-        <v>1.00058913230896</v>
+        <v>1.0003000497817993</v>
       </c>
       <c r="C20" s="1">
-        <v>1.3612880706787109</v>
+        <v>0</v>
       </c>
       <c r="D20" s="1">
-        <v>0.99298334121704102</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>16090.2607421875</v>
+        <v>4250400</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>0.95999997854232788</v>
+        <v>0.99980002641677856</v>
       </c>
       <c r="B21" s="1">
-        <v>1.0036656856536865</v>
+        <v>1.0002000331878662</v>
       </c>
       <c r="C21" s="1">
-        <v>1.0338374376296997</v>
-      </c>
-      <c r="D21" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>19800</v>
+        <v>4435200</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>0.95999997854232788</v>
+        <v>0.99989998340606689</v>
       </c>
       <c r="B22" s="1">
-        <v>1.0043463706970215</v>
+        <v>1.0001000165939331</v>
       </c>
       <c r="C22" s="1">
-        <v>1.0240851640701294</v>
+        <v>0</v>
       </c>
       <c r="D22" s="1">
-        <v>0.99298334121704102</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>20004.337890625</v>
+        <v>4620000</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>0.97000002861022949</v>
+        <v>0.99990999698638916</v>
       </c>
       <c r="B23" s="1">
-        <v>1.0045498609542847</v>
+        <v>1.0000900030136108</v>
       </c>
       <c r="C23" s="1">
-        <v>1.051666259765625</v>
+        <v>0</v>
       </c>
       <c r="D23" s="1">
-        <v>0.99298334121704102</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>24465.330078125</v>
+        <v>4804800</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>0.97000002861022949</v>
+        <v>0.99992001056671143</v>
       </c>
       <c r="B24" s="1">
-        <v>1.0007799863815308</v>
+        <v>1.0000799894332886</v>
       </c>
       <c r="C24" s="1">
-        <v>1.0508705377578735</v>
-      </c>
-      <c r="D24" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>24000</v>
+        <v>4989600</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>0.98000001907348633</v>
+        <v>0.99993002414703369</v>
       </c>
       <c r="B25" s="1">
-        <v>1.005030632019043</v>
+        <v>1.0000699758529663</v>
       </c>
       <c r="C25" s="1">
-        <v>0.99506682157516479</v>
+        <v>0</v>
       </c>
       <c r="D25" s="1">
-        <v>0.99298334121704102</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>34621.84375</v>
+        <v>5174400</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>0.98000001907348633</v>
+        <v>0.99993997812271118</v>
       </c>
       <c r="B26" s="1">
-        <v>1.0047142505645752</v>
+        <v>1.0000600814819336</v>
       </c>
       <c r="C26" s="1">
-        <v>0.99670535326004028</v>
-      </c>
-      <c r="D26" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>33720</v>
+        <v>5359200</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <v>0.99000000953674316</v>
+        <v>0.99994999170303345</v>
       </c>
       <c r="B27" s="1">
-        <v>1.0049300193786621</v>
+        <v>1.0000500679016113</v>
       </c>
       <c r="C27" s="1">
-        <v>1.2578854560852051</v>
+        <v>0</v>
       </c>
       <c r="D27" s="1">
-        <v>0.99298334121704102</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>56667.41796875</v>
+        <v>5544000</v>
       </c>
       <c r="G27" s="1"/>
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <v>0.99000000953674316</v>
+        <v>0.99996000528335571</v>
       </c>
       <c r="B28" s="1">
-        <v>1.0046226978302002</v>
+        <v>1.0000400543212891</v>
       </c>
       <c r="C28" s="1">
-        <v>1.1818376779556274</v>
-      </c>
-      <c r="D28" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>55200</v>
+        <v>5728800</v>
       </c>
       <c r="G28" s="1"/>
     </row>
     <row r="29">
       <c r="A29" s="1">
-        <v>0.99099999666213989</v>
+        <v>0.99997001886367798</v>
       </c>
       <c r="B29" s="1">
-        <v>1.0043056011199951</v>
+        <v>1.0000300407409668</v>
       </c>
       <c r="C29" s="1">
-        <v>0.84707224369049072</v>
-      </c>
-      <c r="D29" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1">
-        <v>60000</v>
+        <v>5913600</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <v>0.99099999666213989</v>
+        <v>0.99997997283935547</v>
       </c>
       <c r="B30" s="1">
-        <v>1.0051852464675903</v>
+        <v>1.0000200271606445</v>
       </c>
       <c r="C30" s="1">
-        <v>0.67989999055862427</v>
+        <v>0</v>
       </c>
       <c r="D30" s="1">
-        <v>0.8200380802154541</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1">
-        <v>61649.71484375</v>
+        <v>6098400</v>
       </c>
       <c r="G30" s="1"/>
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <v>0.99199998378753662</v>
+        <v>0.99998998641967773</v>
       </c>
       <c r="B31" s="1">
-        <v>1.0045413970947266</v>
+        <v>1.0000100135803223</v>
       </c>
       <c r="C31" s="1">
-        <v>0.87893277406692505</v>
-      </c>
-      <c r="D31" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1">
-        <v>66000</v>
+        <v>6283200</v>
       </c>
       <c r="G31" s="1"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>0.99199998378753662</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1.0048574209213257</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0.96017611026763916</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0.8200380802154541</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>68051.3359375</v>
-      </c>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1">
-        <v>0.99299997091293335</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1.0041824579238892</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.59800690412521362</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>72000</v>
-      </c>
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1">
-        <v>0.99299997091293335</v>
-      </c>
-      <c r="B34" s="1">
-        <v>1.0048123598098755</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0.4507327675819397</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0.4507327675819397</v>
-      </c>
-      <c r="E34" s="1">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1">
-        <v>75628.7734375</v>
-      </c>
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1">
-        <v>0.99400001764297485</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1.004254937171936</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.30966874957084656</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.37813195586204529</v>
-      </c>
-      <c r="E35" s="1">
-        <v>0</v>
-      </c>
-      <c r="F35" s="1">
-        <v>83000.9921875</v>
-      </c>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1">
-        <v>0.99400001764297485</v>
-      </c>
-      <c r="B36" s="1">
-        <v>1.0041120052337646</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0.34989017248153687</v>
-      </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1">
-        <v>0</v>
-      </c>
-      <c r="F36" s="1">
-        <v>81000</v>
-      </c>
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1">
-        <v>0.99500000476837158</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1.0035568475723267</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0.44659516215324402</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.37813195586204529</v>
-      </c>
-      <c r="E37" s="1">
-        <v>0</v>
-      </c>
-      <c r="F37" s="1">
-        <v>89064.015625</v>
-      </c>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1">
-        <v>0.99500000476837158</v>
-      </c>
-      <c r="B38" s="1">
-        <v>1.0034700632095337</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0.40817523002624512</v>
-      </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="1">
-        <v>87000</v>
-      </c>
-      <c r="G38" s="1"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1">
-        <v>0.99599999189376831</v>
-      </c>
-      <c r="B39" s="1">
-        <v>1.0028424263000488</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0.36130577325820923</v>
-      </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1">
-        <v>0</v>
-      </c>
-      <c r="F39" s="1">
-        <v>96000</v>
-      </c>
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1">
-        <v>0.99599999189376831</v>
-      </c>
-      <c r="B40" s="1">
-        <v>1.0029977560043335</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0.32759097218513489</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0.33309832215309143</v>
-      </c>
-      <c r="E40" s="1">
-        <v>0</v>
-      </c>
-      <c r="F40" s="1">
-        <v>97621.828125</v>
-      </c>
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1">
-        <v>0.99699997901916504</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1.0021812915802002</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0.33550664782524109</v>
-      </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1">
-        <v>0</v>
-      </c>
-      <c r="F41" s="1">
-        <v>108000</v>
-      </c>
-      <c r="G41" s="1"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1">
-        <v>0.99699997901916504</v>
-      </c>
-      <c r="B42" s="1">
-        <v>1.0023202896118164</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.33860567212104797</v>
-      </c>
-      <c r="D42" s="1">
-        <v>0.33309832215309143</v>
-      </c>
-      <c r="E42" s="1">
-        <v>0</v>
-      </c>
-      <c r="F42" s="1">
-        <v>114298.25</v>
-      </c>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1">
-        <v>0.99800002574920654</v>
-      </c>
-      <c r="B43" s="1">
-        <v>1.0016552209854126</v>
-      </c>
-      <c r="C43" s="1">
-        <v>0.23396006226539612</v>
-      </c>
-      <c r="D43" s="1">
-        <v>0.23396006226539612</v>
-      </c>
-      <c r="E43" s="1">
-        <v>0</v>
-      </c>
-      <c r="F43" s="1">
-        <v>146776.625</v>
-      </c>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1">
-        <v>0.99800002574920654</v>
-      </c>
-      <c r="B44" s="1">
-        <v>1.0015594959259033</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.26331737637519836</v>
-      </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1">
-        <v>0</v>
-      </c>
-      <c r="F44" s="1">
-        <v>133200</v>
-      </c>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1">
-        <v>0.99900001287460327</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1.0008867979049683</v>
-      </c>
-      <c r="C45" s="1">
-        <v>0.21671941876411438</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0.22939594089984894</v>
-      </c>
-      <c r="E45" s="1">
-        <v>0</v>
-      </c>
-      <c r="F45" s="1">
-        <v>203117.78125</v>
-      </c>
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1">
-        <v>0.99900001287460327</v>
-      </c>
-      <c r="B46" s="1">
-        <v>1.0008218288421631</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0.23396006226539612</v>
-      </c>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1">
-        <v>0</v>
-      </c>
-      <c r="F46" s="1">
-        <v>182400</v>
-      </c>
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1">
-        <v>0.99910002946853638</v>
-      </c>
-      <c r="B47" s="1">
-        <v>1.0008082389831543</v>
-      </c>
-      <c r="C47" s="1">
-        <v>0.23303942382335663</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0.22939594089984894</v>
-      </c>
-      <c r="E47" s="1">
-        <v>0</v>
-      </c>
-      <c r="F47" s="1">
-        <v>214148.0625</v>
-      </c>
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1">
-        <v>0.99910002946853638</v>
-      </c>
-      <c r="B48" s="1">
-        <v>1.0007408857345581</v>
-      </c>
-      <c r="C48" s="1">
-        <v>0.23396006226539612</v>
-      </c>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1">
-        <v>0</v>
-      </c>
-      <c r="F48" s="1">
-        <v>186000</v>
-      </c>
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1">
-        <v>0.99919998645782471</v>
-      </c>
-      <c r="B49" s="1">
-        <v>1.0006692409515381</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0.2292163074016571</v>
-      </c>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1">
-        <v>0</v>
-      </c>
-      <c r="F49" s="1">
-        <v>198000</v>
-      </c>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1">
-        <v>0.99919998645782471</v>
-      </c>
-      <c r="B50" s="1">
-        <v>1.000731348991394</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.23842896521091461</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.22939594089984894</v>
-      </c>
-      <c r="E50" s="1">
-        <v>0</v>
-      </c>
-      <c r="F50" s="1">
-        <v>228259.765625</v>
-      </c>
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1">
-        <v>0.99930000305175781</v>
-      </c>
-      <c r="B51" s="1">
-        <v>1.0006550550460815</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.024435019120573997</v>
-      </c>
-      <c r="D51" s="1">
-        <v>0.081451967358589172</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0</v>
-      </c>
-      <c r="F51" s="1">
-        <v>247470.5</v>
-      </c>
-      <c r="G51" s="1"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1">
-        <v>0.99930000305175781</v>
-      </c>
-      <c r="B52" s="1">
-        <v>1.0005922317504883</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.22038343548774719</v>
-      </c>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="1">
-        <v>208800</v>
-      </c>
-      <c r="G52" s="1"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1">
-        <v>0.99940001964569092</v>
-      </c>
-      <c r="B53" s="1">
-        <v>1.0005574226379395</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0.11425475031137466</v>
-      </c>
-      <c r="D53" s="1">
-        <v>0.081451967358589172</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
-      <c r="F53" s="1">
-        <v>276670.71875</v>
-      </c>
-      <c r="G53" s="1"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1">
-        <v>0.99940001964569092</v>
-      </c>
-      <c r="B54" s="1">
-        <v>1.0005127191543579</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0.23366893827915192</v>
-      </c>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1">
-        <v>0</v>
-      </c>
-      <c r="F54" s="1">
-        <v>214440</v>
-      </c>
-      <c r="G54" s="1"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1">
-        <v>0.99949997663497925</v>
-      </c>
-      <c r="B55" s="1">
-        <v>1.0004335641860962</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0.16340522468090057</v>
-      </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1">
-        <v>0</v>
-      </c>
-      <c r="F55" s="1">
-        <v>238800</v>
-      </c>
-      <c r="G55" s="1"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1">
-        <v>0.99949997663497925</v>
-      </c>
-      <c r="B56" s="1">
-        <v>1.0005002021789551</v>
-      </c>
-      <c r="C56" s="1">
-        <v>0</v>
-      </c>
-      <c r="D56" s="1">
-        <v>0.081451967358589172</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0</v>
-      </c>
-      <c r="F56" s="1">
-        <v>325528.1875</v>
-      </c>
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1">
-        <v>0.99959999322891235</v>
-      </c>
-      <c r="B57" s="1">
-        <v>1.0003559589385986</v>
-      </c>
-      <c r="C57" s="1">
-        <v>0.054464317858219147</v>
-      </c>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1">
-        <v>0</v>
-      </c>
-      <c r="F57" s="1">
-        <v>276000</v>
-      </c>
-      <c r="G57" s="1"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1">
-        <v>0.99959999322891235</v>
-      </c>
-      <c r="B58" s="1">
-        <v>1.0003687143325806</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0.18711809813976288</v>
-      </c>
-      <c r="D58" s="1">
-        <v>0.081451967358589172</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0</v>
-      </c>
-      <c r="F58" s="1">
-        <v>337831.875</v>
-      </c>
-      <c r="G58" s="1"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1">
-        <v>0.99970000982284546</v>
-      </c>
-      <c r="B59" s="1">
-        <v>1.0002872943878174</v>
-      </c>
-      <c r="C59" s="1">
-        <v>0.079255104064941406</v>
-      </c>
-      <c r="D59" s="1">
-        <v>0.079255104064941406</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0</v>
-      </c>
-      <c r="F59" s="1">
-        <v>377730.03125</v>
-      </c>
-      <c r="G59" s="1"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1">
-        <v>0.99970000982284546</v>
-      </c>
-      <c r="B60" s="1">
-        <v>1.000257134437561</v>
-      </c>
-      <c r="C60" s="1">
-        <v>0.1364540308713913</v>
-      </c>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1">
-        <v>0</v>
-      </c>
-      <c r="F60" s="1">
-        <v>294960</v>
-      </c>
-      <c r="G60" s="1"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="1">
-        <v>0.99980002641677856</v>
-      </c>
-      <c r="B61" s="1">
-        <v>1.0002000331878662</v>
-      </c>
-      <c r="C61" s="1">
-        <v>0</v>
-      </c>
-      <c r="D61" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0</v>
-      </c>
-      <c r="F61" s="1">
-        <v>484064</v>
-      </c>
-      <c r="G61" s="1"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1">
-        <v>0.99980002641677856</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1.0001697540283203</v>
-      </c>
-      <c r="C62" s="1">
-        <v>0.15868249535560608</v>
-      </c>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1">
-        <v>0</v>
-      </c>
-      <c r="F62" s="1">
-        <v>360000</v>
-      </c>
-      <c r="G62" s="1"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1">
-        <v>0.99989998340606689</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1.0001000165939331</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0</v>
-      </c>
-      <c r="D63" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0</v>
-      </c>
-      <c r="F63" s="1">
-        <v>773111.625</v>
-      </c>
-      <c r="G63" s="1"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1">
-        <v>0.99990999698638916</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1.0000791549682617</v>
-      </c>
-      <c r="C64" s="1">
-        <v>0.079255104064941406</v>
-      </c>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1">
-        <v>0</v>
-      </c>
-      <c r="F64" s="1">
-        <v>391200</v>
-      </c>
-      <c r="G64" s="1"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="1">
-        <v>0.99990999698638916</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1.0000900030136108</v>
-      </c>
-      <c r="C65" s="1">
-        <v>0</v>
-      </c>
-      <c r="D65" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0</v>
-      </c>
-      <c r="F65" s="1">
-        <v>830354.4375</v>
-      </c>
-      <c r="G65" s="1"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="1">
-        <v>0.99992001056671143</v>
-      </c>
-      <c r="B66" s="1">
-        <v>1.0000799894332886</v>
-      </c>
-      <c r="C66" s="1">
-        <v>0</v>
-      </c>
-      <c r="D66" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="1">
-        <v>899481.5</v>
-      </c>
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1">
-        <v>0.99993002414703369</v>
-      </c>
-      <c r="B67" s="1">
-        <v>1.0000699758529663</v>
-      </c>
-      <c r="C67" s="1">
-        <v>0</v>
-      </c>
-      <c r="D67" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1">
-        <v>985662.0625</v>
-      </c>
-      <c r="G67" s="1"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1">
-        <v>0.99993997812271118</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1.000059962272644</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0</v>
-      </c>
-      <c r="D68" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0</v>
-      </c>
-      <c r="F68" s="1">
-        <v>1098027.375</v>
-      </c>
-      <c r="G68" s="1"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="1">
-        <v>0.99994999170303345</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1.0000499486923218</v>
-      </c>
-      <c r="C69" s="1">
-        <v>0</v>
-      </c>
-      <c r="D69" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0</v>
-      </c>
-      <c r="F69" s="1">
-        <v>1252426.625</v>
-      </c>
-      <c r="G69" s="1"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="1">
-        <v>0.99996000528335571</v>
-      </c>
-      <c r="B70" s="1">
-        <v>1.0000400543212891</v>
-      </c>
-      <c r="C70" s="1">
-        <v>0</v>
-      </c>
-      <c r="D70" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
-      <c r="F70" s="1">
-        <v>1478102.875</v>
-      </c>
-      <c r="G70" s="1"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1">
-        <v>0.99997001886367798</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1.0000251531600952</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.48264589905738831</v>
-      </c>
-      <c r="D71" s="1">
-        <v>0.026813661679625511</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="F71" s="1">
-        <v>1834026.5</v>
-      </c>
-      <c r="G71" s="1"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="1">
-        <v>0.99997001886367798</v>
-      </c>
-      <c r="B72" s="1">
-        <v>1.0000239610671997</v>
-      </c>
-      <c r="C72" s="1">
-        <v>0.079255104064941406</v>
-      </c>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1">
-        <v>0</v>
-      </c>
-      <c r="F72" s="1">
-        <v>456000</v>
-      </c>
-      <c r="G72" s="1"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1">
-        <v>0.99997997283935547</v>
-      </c>
-      <c r="B73" s="1">
-        <v>1.0000152587890625</v>
-      </c>
-      <c r="C73" s="1">
-        <v>0.48264589905738831</v>
-      </c>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1">
-        <v>0</v>
-      </c>
-      <c r="F73" s="1">
-        <v>1848000</v>
-      </c>
-      <c r="G73" s="1"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="1">
-        <v>0.99997997283935547</v>
-      </c>
-      <c r="B74" s="1">
-        <v>1.0000200271606445</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0</v>
-      </c>
-      <c r="D74" s="1">
-        <v>0</v>
-      </c>
-      <c r="E74" s="1">
-        <v>0</v>
-      </c>
-      <c r="F74" s="1">
-        <v>2502549</v>
-      </c>
-      <c r="G74" s="1"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1">
-        <v>0.99998998641967773</v>
-      </c>
-      <c r="B75" s="1">
-        <v>1.0000100135803223</v>
-      </c>
-      <c r="C75" s="1">
-        <v>0</v>
-      </c>
-      <c r="D75" s="1">
-        <v>0</v>
-      </c>
-      <c r="E75" s="1">
-        <v>0</v>
-      </c>
-      <c r="F75" s="1">
-        <v>4141491</v>
-      </c>
-      <c r="G75" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -15679,7 +14810,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15707,22 +14838,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>0.95999997854232788</v>
+        <v>0.99500000476837158</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1.003908634185791</v>
       </c>
       <c r="C2" s="1">
-        <v>91.370437622070312</v>
+        <v>0.36255764961242676</v>
       </c>
       <c r="D2" s="1">
-        <v>91.370437622070312</v>
+        <v>0.36255764961242676</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>46823200</v>
       </c>
       <c r="G2" s="1">
         <v>0.99500000476837158</v>
@@ -15730,388 +14861,388 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>0.97000002861022949</v>
+        <v>0.99599999189376831</v>
       </c>
       <c r="B3" s="1">
-        <v>0.94196796417236328</v>
+        <v>1.0032647848129272</v>
       </c>
       <c r="C3" s="1">
-        <v>5.2035708427429199</v>
+        <v>0.27674007415771484</v>
       </c>
       <c r="D3" s="1">
-        <v>5.2035708427429199</v>
+        <v>0.27674007415771484</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>1117734</v>
+        <v>60999996</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>0.98000001907348633</v>
+        <v>0.99699997901916504</v>
       </c>
       <c r="B4" s="1">
-        <v>0.98545360565185547</v>
+        <v>1.0025360584259033</v>
       </c>
       <c r="C4" s="1">
-        <v>2.4852044582366943</v>
+        <v>0.22319909930229187</v>
       </c>
       <c r="D4" s="1">
-        <v>2.4998536109924316</v>
+        <v>0.24164377152919769</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>4134800</v>
+        <v>69200000</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>0.99000000953674316</v>
+        <v>0.99800002574920654</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0006026029586792</v>
+        <v>1.0017551183700562</v>
       </c>
       <c r="C5" s="1">
-        <v>2.6463475227355957</v>
+        <v>0.24835091829299927</v>
       </c>
       <c r="D5" s="1">
-        <v>2.4998536109924316</v>
+        <v>0.24164377152919769</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>11381596</v>
+        <v>76054656</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>0.99099999666213989</v>
+        <v>0.99900001287460327</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0022633075714111</v>
+        <v>1.0010010004043579</v>
       </c>
       <c r="C6" s="1">
-        <v>1.1384719610214233</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>1.2963095903396606</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>12972082</v>
+        <v>360000000</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>0.99199998378753662</v>
+        <v>0.99910002946853638</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0024006366729736</v>
+        <v>1.0009007453918457</v>
       </c>
       <c r="C7" s="1">
-        <v>1.0815640687942505</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>1.2963095903396606</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>14985033</v>
+        <v>384000000</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99919998645782471</v>
       </c>
       <c r="B8" s="1">
-        <v>1.0024803876876831</v>
+        <v>1.000800609588623</v>
       </c>
       <c r="C8" s="1">
-        <v>1.6688704490661621</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>1.2963095903396606</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>17548476</v>
+        <v>408000000</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>0.99400001764297485</v>
+        <v>0.99930000305175781</v>
       </c>
       <c r="B9" s="1">
-        <v>1.0031508207321167</v>
+        <v>1.0007004737854004</v>
       </c>
       <c r="C9" s="1">
-        <v>1.1201208829879761</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>1.1201208829879761</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>20872546</v>
+        <v>432000000</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>0.99500000476837158</v>
+        <v>0.99940001964569092</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0032683610916138</v>
+        <v>1.0006003379821777</v>
       </c>
       <c r="C10" s="1">
-        <v>0.49917209148406982</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>0.49917209148406982</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>25559058</v>
+        <v>456000000</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>0.99599999189376831</v>
+        <v>0.99949997663497925</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0027621984481812</v>
+        <v>1.0005003213882446</v>
       </c>
       <c r="C11" s="1">
-        <v>0.4424901008605957</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>0.44560161232948303</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>32412492</v>
+        <v>480000000</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>0.99699997901916504</v>
+        <v>0.99959999322891235</v>
       </c>
       <c r="B12" s="1">
-        <v>1.0022002458572388</v>
+        <v>1.000400185585022</v>
       </c>
       <c r="C12" s="1">
-        <v>0.44871294498443604</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>0.44560161232948303</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>43360088</v>
+        <v>504000000</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>0.99800002574920654</v>
+        <v>0.99970000982284546</v>
       </c>
       <c r="B13" s="1">
-        <v>1.0016456842422485</v>
+        <v>1.0003000497817993</v>
       </c>
       <c r="C13" s="1">
-        <v>0.21162162721157074</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>0.23100137710571289</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>63592788</v>
+        <v>528000000</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>0.99900001287460327</v>
+        <v>0.99980002641677856</v>
       </c>
       <c r="B14" s="1">
-        <v>1.0010010004043579</v>
+        <v>1.0002000331878662</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>0.23100137710571289</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>110450512</v>
+        <v>552000000</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>0.99910002946853638</v>
+        <v>0.99989998340606689</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0007545948028564</v>
+        <v>1.0001000165939331</v>
       </c>
       <c r="C15" s="1">
-        <v>0.64852994680404663</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>0.23100137710571289</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>119580656</v>
+        <v>576000000</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>0.99919998645782471</v>
+        <v>0.99990999698638916</v>
       </c>
       <c r="B16" s="1">
-        <v>1.000719428062439</v>
+        <v>1.0000900030136108</v>
       </c>
       <c r="C16" s="1">
-        <v>0.23848593235015869</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1">
-        <v>0.23100137710571289</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>130248560</v>
+        <v>600000000</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>0.99930000305175781</v>
+        <v>0.99992001056671143</v>
       </c>
       <c r="B17" s="1">
-        <v>1.0007004737854004</v>
+        <v>1.0000799894332886</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
       </c>
       <c r="D17" s="1">
-        <v>0.14334568381309509</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>143196736</v>
+        <v>624000000</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>0.99940001964569092</v>
+        <v>0.99993002414703369</v>
       </c>
       <c r="B18" s="1">
-        <v>1.0006003379821777</v>
+        <v>1.0000699758529663</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
       </c>
       <c r="D18" s="1">
-        <v>0.14334568381309509</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>159346528</v>
+        <v>648000000</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>0.99949997663497925</v>
+        <v>0.99993997812271118</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0004428625106812</v>
+        <v>1.0000600814819336</v>
       </c>
       <c r="C19" s="1">
-        <v>0.037558142095804214</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1">
-        <v>0.14334568381309509</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>177970736</v>
+        <v>672000000</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>0.99959999322891235</v>
+        <v>0.99994999170303345</v>
       </c>
       <c r="B20" s="1">
-        <v>1.0003465414047241</v>
+        <v>1.0000500679016113</v>
       </c>
       <c r="C20" s="1">
-        <v>0.53573918342590332</v>
+        <v>0</v>
       </c>
       <c r="D20" s="1">
-        <v>0.14334568381309509</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>205028448</v>
+        <v>696000000</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>0.99970000982284546</v>
+        <v>0.99996000528335571</v>
       </c>
       <c r="B21" s="1">
-        <v>1.0003000497817993</v>
+        <v>1.0000400543212891</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -16123,16 +15254,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>245001184</v>
+        <v>720000000</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>0.99980002641677856</v>
+        <v>0.99997001886367798</v>
       </c>
       <c r="B22" s="1">
-        <v>1.0002000331878662</v>
+        <v>1.0000300407409668</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
@@ -16144,16 +15275,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>313092480</v>
+        <v>744000000</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>0.99989998340606689</v>
+        <v>0.99997997283935547</v>
       </c>
       <c r="B23" s="1">
-        <v>1.0001000165939331</v>
+        <v>1.0000200271606445</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
@@ -16165,16 +15296,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>467409984</v>
+        <v>768000000</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>0.99990999698638916</v>
+        <v>0.99998998641967773</v>
       </c>
       <c r="B24" s="1">
-        <v>1.0000900030136108</v>
+        <v>1.0000100135803223</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -16186,177 +15317,9 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>499056192</v>
+        <v>792000000</v>
       </c>
       <c r="G24" s="1"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1">
-        <v>0.99992001056671143</v>
-      </c>
-      <c r="B25" s="1">
-        <v>1.0000799894332886</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
-        <v>533007840</v>
-      </c>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>0.99993002414703369</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.0000699758529663</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>569096384</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>0.99993997812271118</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1.0000600814819336</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>623335232</v>
-      </c>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>0.99994999170303345</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1.0000500679016113</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>678612672</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>0.99996000528335571</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.0000400543212891</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>777354304</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1">
-        <v>0.99997001886367798</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1.0000300407409668</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>910464448</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>0.99997997283935547</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1.0000200271606445</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1103723392</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>0.99998998641967773</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1.0000100135803223</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1634117888</v>
-      </c>
-      <c r="G32" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -16364,7 +15327,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16392,411 +15355,411 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>0.95999997854232788</v>
+        <v>0.99400001764297485</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1.0045983791351318</v>
       </c>
       <c r="C2" s="1">
-        <v>92.4969482421875</v>
+        <v>0.34047451615333557</v>
       </c>
       <c r="D2" s="1">
-        <v>92.4969482421875</v>
+        <v>0.41853168606758118</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>54000000</v>
       </c>
       <c r="G2" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99400001764297485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>0.97000002861022949</v>
+        <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>0.95358157157897949</v>
+        <v>1.003930926322937</v>
       </c>
       <c r="C3" s="1">
-        <v>4.150266170501709</v>
+        <v>0.46110832691192627</v>
       </c>
       <c r="D3" s="1">
-        <v>4.150266170501709</v>
+        <v>0.41853168606758118</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>1587500</v>
+        <v>58321200</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>0.98000001907348633</v>
+        <v>0.99599999189376831</v>
       </c>
       <c r="B4" s="1">
-        <v>0.98620074987411499</v>
+        <v>1.0033860206604004</v>
       </c>
       <c r="C4" s="1">
-        <v>2.5335080623626709</v>
+        <v>0.24041056632995605</v>
       </c>
       <c r="D4" s="1">
-        <v>2.5335080623626709</v>
+        <v>0.24041056632995605</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>4785950</v>
+        <v>71050000</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>0.99000000953674316</v>
+        <v>0.99699997901916504</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0018301010131836</v>
+        <v>1.0026206970214844</v>
       </c>
       <c r="C5" s="1">
-        <v>1.4117783308029175</v>
+        <v>0.19283121824264526</v>
       </c>
       <c r="D5" s="1">
-        <v>1.4230718612670898</v>
+        <v>0.19373804330825806</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>12554216</v>
+        <v>75855000</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>0.99099999666213989</v>
+        <v>0.99800002574920654</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0022437572479248</v>
+        <v>1.0018092393875122</v>
       </c>
       <c r="C6" s="1">
-        <v>1.1944183111190796</v>
+        <v>0.19434258341789246</v>
       </c>
       <c r="D6" s="1">
-        <v>1.4230718612670898</v>
+        <v>0.19373804330825806</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>14332700</v>
+        <v>84000000</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>0.99199998378753662</v>
+        <v>0.99900001287460327</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0024374723434448</v>
+        <v>1.0010010004043579</v>
       </c>
       <c r="C7" s="1">
-        <v>1.6630189418792725</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>1.4230718612670898</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>16412220</v>
+        <v>360000000</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99910002946853638</v>
       </c>
       <c r="B8" s="1">
-        <v>1.0031026601791382</v>
+        <v>1.0009007453918457</v>
       </c>
       <c r="C8" s="1">
-        <v>0.73108166456222534</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>0.89543169736862183</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>19151954</v>
+        <v>384000000</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>0.99400001764297485</v>
+        <v>0.99919998645782471</v>
       </c>
       <c r="B9" s="1">
-        <v>1.0028289556503296</v>
+        <v>1.000800609588623</v>
       </c>
       <c r="C9" s="1">
-        <v>1.0597915649414062</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>0.89543169736862183</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>22824014</v>
+        <v>408000000</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>0.99500000476837158</v>
+        <v>0.99930000305175781</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0028862953186035</v>
+        <v>1.0007004737854004</v>
       </c>
       <c r="C10" s="1">
-        <v>0.61063468456268311</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>0.61063468456268311</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>27682104</v>
+        <v>432000000</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>0.99599999189376831</v>
+        <v>0.99940001964569092</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0024924278259277</v>
+        <v>1.0006003379821777</v>
       </c>
       <c r="C11" s="1">
-        <v>0.46059653162956238</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>0.481557697057724</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>35012492</v>
+        <v>456000000</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>0.99699997901916504</v>
+        <v>0.99949997663497925</v>
       </c>
       <c r="B12" s="1">
-        <v>1.0019489526748657</v>
+        <v>1.0005003213882446</v>
       </c>
       <c r="C12" s="1">
-        <v>0.46213307976722717</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>0.481557697057724</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>46591312</v>
+        <v>480000000</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>0.99800002574920654</v>
+        <v>0.99959999322891235</v>
       </c>
       <c r="B13" s="1">
-        <v>1.0014079809188843</v>
+        <v>1.000400185585022</v>
       </c>
       <c r="C13" s="1">
-        <v>0.52194464206695557</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>0.481557697057724</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>67645824</v>
+        <v>504000000</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>0.99900001287460327</v>
+        <v>0.99970000982284546</v>
       </c>
       <c r="B14" s="1">
-        <v>1.0010010004043579</v>
+        <v>1.0003000497817993</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>0.10405681282281876</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>117282376</v>
+        <v>528000000</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>0.99910002946853638</v>
+        <v>0.99980002641677856</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0009007453918457</v>
+        <v>1.0002000331878662</v>
       </c>
       <c r="C15" s="1">
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>0.10405681282281876</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>126537112</v>
+        <v>552000000</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>0.99919998645782471</v>
+        <v>0.99989998340606689</v>
       </c>
       <c r="B16" s="1">
-        <v>1.000800609588623</v>
+        <v>1.0001000165939331</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
       </c>
       <c r="D16" s="1">
-        <v>0.10405681282281876</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>137124896</v>
+        <v>576000000</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>0.99930000305175781</v>
+        <v>0.99990999698638916</v>
       </c>
       <c r="B17" s="1">
-        <v>1.0007004737854004</v>
+        <v>1.0000900030136108</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
       </c>
       <c r="D17" s="1">
-        <v>0.10405681282281876</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>149750848</v>
+        <v>600000000</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>0.99940001964569092</v>
+        <v>0.99992001056671143</v>
       </c>
       <c r="B18" s="1">
-        <v>1.0006003379821777</v>
+        <v>1.0000799894332886</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
       </c>
       <c r="D18" s="1">
-        <v>0.10405681282281876</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>164865536</v>
+        <v>624000000</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>0.99949997663497925</v>
+        <v>0.99993002414703369</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0005003213882446</v>
+        <v>1.0000699758529663</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
       </c>
       <c r="D19" s="1">
-        <v>0.10405681282281876</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>184433152</v>
+        <v>648000000</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>0.99959999322891235</v>
+        <v>0.99993997812271118</v>
       </c>
       <c r="B20" s="1">
-        <v>1.0003273487091064</v>
+        <v>1.0000600814819336</v>
       </c>
       <c r="C20" s="1">
-        <v>0.72827368974685669</v>
+        <v>0</v>
       </c>
       <c r="D20" s="1">
-        <v>0.10405681282281876</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>213027456</v>
+        <v>672000000</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>0.99970000982284546</v>
+        <v>0.99994999170303345</v>
       </c>
       <c r="B21" s="1">
-        <v>1.0003000497817993</v>
+        <v>1.0000500679016113</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -16808,16 +15771,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>255529904</v>
+        <v>696000000</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>0.99980002641677856</v>
+        <v>0.99996000528335571</v>
       </c>
       <c r="B22" s="1">
-        <v>1.0002000331878662</v>
+        <v>1.0000400543212891</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
@@ -16829,16 +15792,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>325732064</v>
+        <v>720000000</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>0.99989998340606689</v>
+        <v>0.99997001886367798</v>
       </c>
       <c r="B23" s="1">
-        <v>1.0001000165939331</v>
+        <v>1.0000300407409668</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
@@ -16850,16 +15813,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>491926944</v>
+        <v>744000000</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>0.99990999698638916</v>
+        <v>0.99997997283935547</v>
       </c>
       <c r="B24" s="1">
-        <v>1.0000900030136108</v>
+        <v>1.0000200271606445</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -16871,16 +15834,16 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>517912064</v>
+        <v>768000000</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>0.99992001056671143</v>
+        <v>0.99998998641967773</v>
       </c>
       <c r="B25" s="1">
-        <v>1.0000799894332886</v>
+        <v>1.0000100135803223</v>
       </c>
       <c r="C25" s="1">
         <v>0</v>
@@ -16892,156 +15855,9 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>549056000</v>
+        <v>792000000</v>
       </c>
       <c r="G25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>0.99993002414703369</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.0000699758529663</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>598243712</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>0.99993997812271118</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1.0000600814819336</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>641217792</v>
-      </c>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>0.99994999170303345</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1.0000500679016113</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>732666176</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>0.99996000528335571</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.0000400543212891</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>842734912</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1">
-        <v>0.99997001886367798</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1.0000300407409668</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>972763072</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>0.99997997283935547</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1.0000200271606445</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1134244864</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>0.99998998641967773</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1.0000100135803223</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1613037184</v>
-      </c>
-      <c r="G32" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -17734,7 +16550,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17762,22 +16578,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>0.94999998807907104</v>
+        <v>0.99400001764297485</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1.0044375658035278</v>
       </c>
       <c r="C2" s="1">
-        <v>87.021514892578125</v>
+        <v>0.35980445146560669</v>
       </c>
       <c r="D2" s="1">
-        <v>87.021514892578125</v>
+        <v>0.425944983959198</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>49400000</v>
       </c>
       <c r="G2" s="1">
         <v>0.99400001764297485</v>
@@ -17785,262 +16601,262 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>0.95999997854232788</v>
+        <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>0.90647321939468384</v>
+        <v>1.0037896633148193</v>
       </c>
       <c r="C3" s="1">
-        <v>6.8855991363525391</v>
+        <v>0.46562927961349487</v>
       </c>
       <c r="D3" s="1">
-        <v>6.8855991363525391</v>
+        <v>0.425944983959198</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>243000</v>
+        <v>56942280</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>0.97000002861022949</v>
+        <v>0.99599999189376831</v>
       </c>
       <c r="B4" s="1">
-        <v>0.96811401844024658</v>
+        <v>1.0032494068145752</v>
       </c>
       <c r="C4" s="1">
-        <v>3.5230722427368164</v>
+        <v>0.3095114529132843</v>
       </c>
       <c r="D4" s="1">
-        <v>3.5230722427368164</v>
+        <v>0.3095114529132843</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>2571317</v>
+        <v>64341960</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>0.98000001907348633</v>
+        <v>0.99699997901916504</v>
       </c>
       <c r="B5" s="1">
-        <v>0.99418503046035767</v>
+        <v>1.0025535821914673</v>
       </c>
       <c r="C5" s="1">
-        <v>1.737046480178833</v>
+        <v>0.19717869162559509</v>
       </c>
       <c r="D5" s="1">
-        <v>1.737046480178833</v>
+        <v>0.23451286554336548</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>6050000</v>
+        <v>72735408</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>0.99000000953674316</v>
+        <v>0.99800002574920654</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0016887187957764</v>
+        <v>1.0017465353012085</v>
       </c>
       <c r="C6" s="1">
-        <v>1.1346708536148071</v>
+        <v>0.25691336393356323</v>
       </c>
       <c r="D6" s="1">
-        <v>1.4373650550842285</v>
+        <v>0.23451286554336548</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>15291200</v>
+        <v>80400000</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>0.99099999666213989</v>
+        <v>0.99900001287460327</v>
       </c>
       <c r="B7" s="1">
-        <v>1.001822829246521</v>
+        <v>1.0010010004043579</v>
       </c>
       <c r="C7" s="1">
-        <v>1.7400593757629395</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>1.4373650550842285</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>17326022</v>
+        <v>139105792</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>0.99199998378753662</v>
+        <v>0.99910002946853638</v>
       </c>
       <c r="B8" s="1">
-        <v>1.0025670528411865</v>
+        <v>1.0009007453918457</v>
       </c>
       <c r="C8" s="1">
-        <v>1.3938833475112915</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>1.4291714429855347</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>19877740</v>
+        <v>148379520</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99919998645782471</v>
       </c>
       <c r="B9" s="1">
-        <v>1.0029610395431519</v>
+        <v>1.000800609588623</v>
       </c>
       <c r="C9" s="1">
-        <v>1.4644575119018555</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>1.4291714429855347</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>23205310</v>
+        <v>157653232</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>0.99400001764297485</v>
+        <v>0.99930000305175781</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0034253597259521</v>
+        <v>1.0007004737854004</v>
       </c>
       <c r="C10" s="1">
-        <v>0.79215830564498901</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>0.79215830564498901</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>27508250</v>
+        <v>166926944</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>0.99500000476837158</v>
+        <v>0.99940001964569092</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0032130479812622</v>
+        <v>1.0006003379821777</v>
       </c>
       <c r="C11" s="1">
-        <v>0.59524857997894287</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>0.67084991931915283</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>33550000</v>
+        <v>176200672</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>0.99599999189376831</v>
+        <v>0.99949997663497925</v>
       </c>
       <c r="B12" s="1">
-        <v>1.0028034448623657</v>
+        <v>1.0005003213882446</v>
       </c>
       <c r="C12" s="1">
-        <v>0.74645119905471802</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>0.67084991931915283</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>42261096</v>
+        <v>185474400</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>0.99699997901916504</v>
+        <v>0.99959999322891235</v>
       </c>
       <c r="B13" s="1">
-        <v>1.0025464296340942</v>
+        <v>1.000400185585022</v>
       </c>
       <c r="C13" s="1">
-        <v>0.30634862184524536</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>0.30634862184524536</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>55793808</v>
+        <v>194748112</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>0.99800002574920654</v>
+        <v>0.99970000982284546</v>
       </c>
       <c r="B14" s="1">
-        <v>1.0018488168716431</v>
+        <v>1.0003000497817993</v>
       </c>
       <c r="C14" s="1">
-        <v>0.15493829548358917</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>0.15493829548358917</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>80125816</v>
+        <v>204021824</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>0.99900001287460327</v>
+        <v>0.99980002641677856</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0010010004043579</v>
+        <v>1.0002000331878662</v>
       </c>
       <c r="C15" s="1">
         <v>0</v>
@@ -18052,16 +16868,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>138596912</v>
+        <v>213295552</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>0.99910002946853638</v>
+        <v>0.99989998340606689</v>
       </c>
       <c r="B16" s="1">
-        <v>1.0009007453918457</v>
+        <v>1.0001000165939331</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
@@ -18073,16 +16889,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>149013408</v>
+        <v>222569280</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>0.99919998645782471</v>
+        <v>0.99990999698638916</v>
       </c>
       <c r="B17" s="1">
-        <v>1.000800609588623</v>
+        <v>1.0000900030136108</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -18094,16 +16910,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>160776544</v>
+        <v>231842992</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>0.99930000305175781</v>
+        <v>0.99992001056671143</v>
       </c>
       <c r="B18" s="1">
-        <v>1.0007004737854004</v>
+        <v>1.0000799894332886</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -18115,16 +16931,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>177065936</v>
+        <v>241116704</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>0.99940001964569092</v>
+        <v>0.99993002414703369</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0006003379821777</v>
+        <v>1.0000699758529663</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -18136,16 +16952,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>195018544</v>
+        <v>250390432</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>0.99949997663497925</v>
+        <v>0.99993997812271118</v>
       </c>
       <c r="B20" s="1">
-        <v>1.0005003213882446</v>
+        <v>1.0000600814819336</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -18157,16 +16973,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>219256576</v>
+        <v>259664160</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>0.99959999322891235</v>
+        <v>0.99994999170303345</v>
       </c>
       <c r="B21" s="1">
-        <v>1.000400185585022</v>
+        <v>1.0000500679016113</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -18178,16 +16994,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>252479792</v>
+        <v>268937856</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>0.99970000982284546</v>
+        <v>0.99996000528335571</v>
       </c>
       <c r="B22" s="1">
-        <v>1.0003000497817993</v>
+        <v>1.0000400543212891</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
@@ -18199,16 +17015,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>305286208</v>
+        <v>278211584</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>0.99980002641677856</v>
+        <v>0.99997001886367798</v>
       </c>
       <c r="B23" s="1">
-        <v>1.0002000331878662</v>
+        <v>1.0000300407409668</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
@@ -18220,16 +17036,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>383426176</v>
+        <v>287485312</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>0.99989998340606689</v>
+        <v>0.99997997283935547</v>
       </c>
       <c r="B24" s="1">
-        <v>1.0001000165939331</v>
+        <v>1.0000200271606445</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -18241,16 +17057,16 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>559635904</v>
+        <v>296759040</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>0.99990999698638916</v>
+        <v>0.99998998641967773</v>
       </c>
       <c r="B25" s="1">
-        <v>1.0000900030136108</v>
+        <v>1.0000100135803223</v>
       </c>
       <c r="C25" s="1">
         <v>0</v>
@@ -18262,177 +17078,9 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>591596288</v>
+        <v>306032768</v>
       </c>
       <c r="G25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>0.99992001056671143</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.0000799894332886</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>639019968</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>0.99993002414703369</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1.0000699758529663</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>686766400</v>
-      </c>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>0.99993997812271118</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1.0000600814819336</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>750400448</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>0.99994999170303345</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.0000500679016113</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>843993984</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1">
-        <v>0.99996000528335571</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1.0000400543212891</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>974023808</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>0.99997001886367798</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1.0000300407409668</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1107574400</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>0.99997997283935547</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1.0000200271606445</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1362693632</v>
-      </c>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1">
-        <v>0.99998998641967773</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1.0000100135803223</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1896250496</v>
-      </c>
-      <c r="G33" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -18440,7 +17088,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18468,285 +17116,285 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>0.94999998807907104</v>
+        <v>0.99400001764297485</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1.0044891834259033</v>
       </c>
       <c r="C2" s="1">
-        <v>88.633064270019531</v>
+        <v>0.38686800003051758</v>
       </c>
       <c r="D2" s="1">
-        <v>88.633064270019531</v>
+        <v>0.39054411649703979</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>46757432</v>
       </c>
       <c r="G2" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99400001764297485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>0.95999997854232788</v>
+        <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>0.9232601523399353</v>
+        <v>1.0038684606552124</v>
       </c>
       <c r="C3" s="1">
-        <v>5.8033537864685059</v>
+        <v>0.39369508624076843</v>
       </c>
       <c r="D3" s="1">
-        <v>5.8033537864685059</v>
+        <v>0.39054411649703979</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>450000</v>
+        <v>50000000</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>0.97000002861022949</v>
+        <v>0.99599999189376831</v>
       </c>
       <c r="B4" s="1">
-        <v>0.97357070446014404</v>
+        <v>1.0032558441162109</v>
       </c>
       <c r="C4" s="1">
-        <v>3.1041576862335205</v>
+        <v>0.29749530553817749</v>
       </c>
       <c r="D4" s="1">
-        <v>3.1041576862335205</v>
+        <v>0.29749530553817749</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>2900000</v>
+        <v>58000000</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>0.98000001907348633</v>
+        <v>0.99699997901916504</v>
       </c>
       <c r="B5" s="1">
-        <v>0.99531131982803345</v>
+        <v>1.0025479793548584</v>
       </c>
       <c r="C5" s="1">
-        <v>1.6732982397079468</v>
+        <v>0.2014903724193573</v>
       </c>
       <c r="D5" s="1">
-        <v>1.6732982397079468</v>
+        <v>0.23484183847904205</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>6451625</v>
+        <v>61109544</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>0.99000000953674316</v>
+        <v>0.99800002574920654</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0021597146987915</v>
+        <v>1.0017452239990234</v>
       </c>
       <c r="C6" s="1">
-        <v>1.6218619346618652</v>
+        <v>0.25818786025047302</v>
       </c>
       <c r="D6" s="1">
-        <v>1.6218619346618652</v>
+        <v>0.23484183847904205</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>16033167</v>
+        <v>67378392</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>0.99099999666213989</v>
+        <v>0.99900001287460327</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0027849674224854</v>
+        <v>1.0010010004043579</v>
       </c>
       <c r="C7" s="1">
-        <v>1.2867418527603149</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>1.4066928625106812</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>18172500</v>
+        <v>208789568</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>0.99199998378753662</v>
+        <v>0.99910002946853638</v>
       </c>
       <c r="B8" s="1">
-        <v>1.0030711889266968</v>
+        <v>1.0009007453918457</v>
       </c>
       <c r="C8" s="1">
-        <v>1.5266438722610474</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>1.4066928625106812</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>20805400</v>
+        <v>222708864</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99919998645782471</v>
       </c>
       <c r="B9" s="1">
-        <v>1.0035984516143799</v>
+        <v>1.000800609588623</v>
       </c>
       <c r="C9" s="1">
-        <v>0.73356670141220093</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>0.8919183611869812</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>24267290</v>
+        <v>236628176</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>0.99400001764297485</v>
+        <v>0.99930000305175781</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0033267736434937</v>
+        <v>1.0007004737854004</v>
       </c>
       <c r="C10" s="1">
-        <v>1.0502794981002808</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>0.8919183611869812</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>28759904</v>
+        <v>250547488</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>0.99500000476837158</v>
+        <v>0.99940001964569092</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0033739805221558</v>
+        <v>1.0006003379821777</v>
       </c>
       <c r="C11" s="1">
-        <v>0.80813825130462646</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>0.80813825130462646</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>34862256</v>
+        <v>264466784</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>0.99599999189376831</v>
+        <v>0.99949997663497925</v>
       </c>
       <c r="B12" s="1">
-        <v>1.0031780004501343</v>
+        <v>1.0005003213882446</v>
       </c>
       <c r="C12" s="1">
-        <v>0.49898418784141541</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>0.49898418784141541</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>43728424</v>
+        <v>278386080</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>0.99699997901916504</v>
+        <v>0.99959999322891235</v>
       </c>
       <c r="B13" s="1">
-        <v>1.0026723146438599</v>
+        <v>1.000400185585022</v>
       </c>
       <c r="C13" s="1">
-        <v>0.28459200263023376</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>0.28459200263023376</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>57995500</v>
+        <v>292305408</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>0.99800002574920654</v>
+        <v>0.99970000982284546</v>
       </c>
       <c r="B14" s="1">
-        <v>1.0019527673721313</v>
+        <v>1.0003000497817993</v>
       </c>
       <c r="C14" s="1">
-        <v>0.051153279840946198</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>0.051153279840946198</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>83462584</v>
+        <v>306224704</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>0.99900001287460327</v>
+        <v>0.99980002641677856</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0010010004043579</v>
+        <v>1.0002000331878662</v>
       </c>
       <c r="C15" s="1">
         <v>0</v>
@@ -18758,16 +17406,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>143460448</v>
+        <v>320144000</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>0.99910002946853638</v>
+        <v>0.99989998340606689</v>
       </c>
       <c r="B16" s="1">
-        <v>1.0009007453918457</v>
+        <v>1.0001000165939331</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
@@ -18779,16 +17427,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>155235232</v>
+        <v>334063296</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>0.99919998645782471</v>
+        <v>0.99990999698638916</v>
       </c>
       <c r="B17" s="1">
-        <v>1.000800609588623</v>
+        <v>1.0000900030136108</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -18800,16 +17448,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>169208864</v>
+        <v>347982592</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>0.99930000305175781</v>
+        <v>0.99992001056671143</v>
       </c>
       <c r="B18" s="1">
-        <v>1.0007004737854004</v>
+        <v>1.0000799894332886</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -18821,16 +17469,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>183750576</v>
+        <v>361901920</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>0.99940001964569092</v>
+        <v>0.99993002414703369</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0006003379821777</v>
+        <v>1.0000699758529663</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -18842,16 +17490,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>202268448</v>
+        <v>375821216</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>0.99949997663497925</v>
+        <v>0.99993997812271118</v>
       </c>
       <c r="B20" s="1">
-        <v>1.0005003213882446</v>
+        <v>1.0000600814819336</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -18863,16 +17511,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>225534768</v>
+        <v>389740512</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>0.99959999322891235</v>
+        <v>0.99994999170303345</v>
       </c>
       <c r="B21" s="1">
-        <v>1.000400185585022</v>
+        <v>1.0000500679016113</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -18884,16 +17532,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>261472608</v>
+        <v>403659840</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>0.99970000982284546</v>
+        <v>0.99996000528335571</v>
       </c>
       <c r="B22" s="1">
-        <v>1.0003000497817993</v>
+        <v>1.0000400543212891</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
@@ -18905,16 +17553,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>315177632</v>
+        <v>417579136</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>0.99980002641677856</v>
+        <v>0.99997001886367798</v>
       </c>
       <c r="B23" s="1">
-        <v>1.0002000331878662</v>
+        <v>1.0000300407409668</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
@@ -18926,16 +17574,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>400534336</v>
+        <v>431498432</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>0.99989998340606689</v>
+        <v>0.99997997283935547</v>
       </c>
       <c r="B24" s="1">
-        <v>1.0001000165939331</v>
+        <v>1.0000200271606445</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -18947,16 +17595,16 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>595235712</v>
+        <v>445417728</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>0.99990999698638916</v>
+        <v>0.99998998641967773</v>
       </c>
       <c r="B25" s="1">
-        <v>1.0000900030136108</v>
+        <v>1.0000100135803223</v>
       </c>
       <c r="C25" s="1">
         <v>0</v>
@@ -18968,177 +17616,9 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>633479936</v>
+        <v>459337024</v>
       </c>
       <c r="G25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>0.99992001056671143</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.0000799894332886</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>677691264</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>0.99993002414703369</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1.0000699758529663</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>723951552</v>
-      </c>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>0.99993997812271118</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1.0000600814819336</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>782626496</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>0.99994999170303345</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.0000500679016113</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>864301440</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1">
-        <v>0.99996000528335571</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1.0000400543212891</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>974857920</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>0.99997001886367798</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1.0000300407409668</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1127942272</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>0.99997997283935547</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1.0000200271606445</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1438166912</v>
-      </c>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1">
-        <v>0.99998998641967773</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1.0000100135803223</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1974907136</v>
-      </c>
-      <c r="G33" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -19146,7 +17626,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19174,285 +17654,285 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>0.94999998807907104</v>
+        <v>0.99400001764297485</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1.0044560432434082</v>
       </c>
       <c r="C2" s="1">
-        <v>90.674850463867188</v>
+        <v>0.34276136755943298</v>
       </c>
       <c r="D2" s="1">
-        <v>90.674850463867188</v>
+        <v>0.39582076668739319</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>53354504</v>
       </c>
       <c r="G2" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99400001764297485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>0.95999997854232788</v>
+        <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>0.94452887773513794</v>
+        <v>1.0037910938262939</v>
       </c>
       <c r="C3" s="1">
-        <v>4.6226387023925781</v>
+        <v>0.4382682740688324</v>
       </c>
       <c r="D3" s="1">
-        <v>4.6226387023925781</v>
+        <v>0.39582076668739319</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>920270</v>
+        <v>60000000</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>0.97000002861022949</v>
+        <v>0.99599999189376831</v>
       </c>
       <c r="B4" s="1">
-        <v>0.98244774341583252</v>
+        <v>1.0032232999801636</v>
       </c>
       <c r="C4" s="1">
-        <v>2.7298445701599121</v>
+        <v>0.32415083050727844</v>
       </c>
       <c r="D4" s="1">
-        <v>2.7298445701599121</v>
+        <v>0.32415083050727844</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>3480000</v>
+        <v>71100000</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>0.98000001907348633</v>
+        <v>0.99699997901916504</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0002782344818115</v>
+        <v>1.0025421380996704</v>
       </c>
       <c r="C5" s="1">
-        <v>1.3369613885879517</v>
+        <v>0.19366089999675751</v>
       </c>
       <c r="D5" s="1">
-        <v>1.3506466150283813</v>
+        <v>0.23533287644386292</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>7296901</v>
+        <v>84768840</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>0.99000000953674316</v>
+        <v>0.99800002574920654</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0036791563034058</v>
+        <v>1.0017316341400146</v>
       </c>
       <c r="C6" s="1">
-        <v>1.4875003099441528</v>
+        <v>0.27179586887359619</v>
       </c>
       <c r="D6" s="1">
-        <v>1.3506466150283813</v>
+        <v>0.23533287644386292</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>17924006</v>
+        <v>94206600</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>0.99099999666213989</v>
+        <v>0.99900001287460327</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0041673183441162</v>
+        <v>1.0010010004043579</v>
       </c>
       <c r="C7" s="1">
-        <v>0.6547437310218811</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>1.0224529504776001</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>20220000</v>
+        <v>304500000</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>0.99199998378753662</v>
+        <v>0.99910002946853638</v>
       </c>
       <c r="B8" s="1">
-        <v>1.0038150548934937</v>
+        <v>1.0009007453918457</v>
       </c>
       <c r="C8" s="1">
-        <v>1.3901622295379639</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>1.0224529504776001</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>23241948</v>
+        <v>324800000</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99919998645782471</v>
       </c>
       <c r="B9" s="1">
-        <v>1.0042041540145874</v>
+        <v>1.000800609588623</v>
       </c>
       <c r="C9" s="1">
-        <v>0.77326488494873047</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>0.77326488494873047</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>26909506</v>
+        <v>345100000</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>0.99400001764297485</v>
+        <v>0.99930000305175781</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0039718151092529</v>
+        <v>1.0007004737854004</v>
       </c>
       <c r="C10" s="1">
-        <v>0.62708914279937744</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>0.62708914279937744</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>31819712</v>
+        <v>365400000</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>0.99500000476837158</v>
+        <v>0.99940001964569092</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0035930871963501</v>
+        <v>1.0006003379821777</v>
       </c>
       <c r="C11" s="1">
-        <v>0.53589808940887451</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>0.53589808940887451</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>38472728</v>
+        <v>385700000</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>0.99599999189376831</v>
+        <v>0.99949997663497925</v>
       </c>
       <c r="B12" s="1">
-        <v>1.00312340259552</v>
+        <v>1.0005003213882446</v>
       </c>
       <c r="C12" s="1">
-        <v>0.46663683652877808</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>0.46663683652877808</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>48224736</v>
+        <v>406000000</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>0.99699997901916504</v>
+        <v>0.99959999322891235</v>
       </c>
       <c r="B13" s="1">
-        <v>1.0025854110717773</v>
+        <v>1.000400185585022</v>
       </c>
       <c r="C13" s="1">
-        <v>0.31012555956840515</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>0.31012555956840515</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>64347200</v>
+        <v>426300000</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>0.99800002574920654</v>
+        <v>0.99970000982284546</v>
       </c>
       <c r="B14" s="1">
-        <v>1.0018914937973022</v>
+        <v>1.0003000497817993</v>
       </c>
       <c r="C14" s="1">
-        <v>0.1122683584690094</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>0.1122683584690094</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>91785472</v>
+        <v>446600000</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>0.99900001287460327</v>
+        <v>0.99980002641677856</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0010010004043579</v>
+        <v>1.0002000331878662</v>
       </c>
       <c r="C15" s="1">
         <v>0</v>
@@ -19464,16 +17944,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>156626336</v>
+        <v>466900000</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>0.99910002946853638</v>
+        <v>0.99989998340606689</v>
       </c>
       <c r="B16" s="1">
-        <v>1.0009007453918457</v>
+        <v>1.0001000165939331</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
@@ -19485,16 +17965,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>168808992</v>
+        <v>487200000</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>0.99919998645782471</v>
+        <v>0.99990999698638916</v>
       </c>
       <c r="B17" s="1">
-        <v>1.000800609588623</v>
+        <v>1.0000900030136108</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -19506,16 +17986,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>183306704</v>
+        <v>507500000</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>0.99930000305175781</v>
+        <v>0.99992001056671143</v>
       </c>
       <c r="B18" s="1">
-        <v>1.0007004737854004</v>
+        <v>1.0000799894332886</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -19527,16 +18007,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>200756832</v>
+        <v>527800000</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>0.99940001964569092</v>
+        <v>0.99993002414703369</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0006003379821777</v>
+        <v>1.0000699758529663</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -19548,16 +18028,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>222285632</v>
+        <v>548099968</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>0.99949997663497925</v>
+        <v>0.99993997812271118</v>
       </c>
       <c r="B20" s="1">
-        <v>1.0005003213882446</v>
+        <v>1.0000600814819336</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -19569,16 +18049,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>249035360</v>
+        <v>568400000</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>0.99959999322891235</v>
+        <v>0.99994999170303345</v>
       </c>
       <c r="B21" s="1">
-        <v>1.000400185585022</v>
+        <v>1.0000500679016113</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -19590,16 +18070,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>285879328</v>
+        <v>588700032</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>0.99970000982284546</v>
+        <v>0.99996000528335571</v>
       </c>
       <c r="B22" s="1">
-        <v>1.0003000497817993</v>
+        <v>1.0000400543212891</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
@@ -19611,16 +18091,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>340198272</v>
+        <v>609000000</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>0.99980002641677856</v>
+        <v>0.99997001886367798</v>
       </c>
       <c r="B23" s="1">
-        <v>1.0002000331878662</v>
+        <v>1.0000300407409668</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
@@ -19632,16 +18112,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>425688416</v>
+        <v>629299968</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>0.99989998340606689</v>
+        <v>0.99997997283935547</v>
       </c>
       <c r="B24" s="1">
-        <v>1.0001000165939331</v>
+        <v>1.0000200271606445</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -19653,16 +18133,16 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>622191488</v>
+        <v>649600000</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>0.99990999698638916</v>
+        <v>0.99998998641967773</v>
       </c>
       <c r="B25" s="1">
-        <v>1.0000900030136108</v>
+        <v>1.0000100135803223</v>
       </c>
       <c r="C25" s="1">
         <v>0</v>
@@ -19674,177 +18154,9 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>669515264</v>
+        <v>669900032</v>
       </c>
       <c r="G25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>0.99992001056671143</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.0000799894332886</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>718801536</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>0.99993002414703369</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1.0000699758529663</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>778643968</v>
-      </c>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>0.99993997812271118</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1.0000600814819336</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>860888640</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>0.99994999170303345</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.0000500679016113</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>939021504</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1">
-        <v>0.99996000528335571</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1.0000400543212891</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1074314112</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>0.99997001886367798</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1.0000300407409668</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1300122368</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>0.99997997283935547</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1.0000200271606445</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1590685312</v>
-      </c>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1">
-        <v>0.99998998641967773</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1.0000100135803223</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2189451776</v>
-      </c>
-      <c r="G33" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -19857,25 +18169,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1207</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1208</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1209</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1210</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1211</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1212</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1213</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -19912,7 +18224,7 @@
         <v>0.74720287322998047</v>
       </c>
       <c r="D3" s="1">
-        <v>0.75990372896194458</v>
+        <v>0.75804883241653442</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -19933,7 +18245,7 @@
         <v>0.36516082286834717</v>
       </c>
       <c r="D4" s="1">
-        <v>0.75990372896194458</v>
+        <v>0.75804883241653442</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -19951,10 +18263,10 @@
         <v>1.004916787147522</v>
       </c>
       <c r="C5" s="1">
-        <v>0.9926220178604126</v>
+        <v>0.97955811023712158</v>
       </c>
       <c r="D5" s="1">
-        <v>0.75990372896194458</v>
+        <v>0.75804883241653442</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -19969,19 +18281,19 @@
         <v>0.99199998378753662</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0049043893814087</v>
+        <v>1.0048911571502686</v>
       </c>
       <c r="C6" s="1">
-        <v>0.59689706563949585</v>
+        <v>0.60996097326278687</v>
       </c>
       <c r="D6" s="1">
-        <v>0.59689706563949585</v>
+        <v>0.60996097326278687</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>63600</v>
+        <v>63300</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -20035,10 +18347,10 @@
         <v>1.0036119222640991</v>
       </c>
       <c r="C9" s="1">
-        <v>0.56534546613693237</v>
+        <v>0.54879170656204224</v>
       </c>
       <c r="D9" s="1">
-        <v>0.56534546613693237</v>
+        <v>0.54879170656204224</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -20053,19 +18365,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0031719207763672</v>
+        <v>1.0031553506851196</v>
       </c>
       <c r="C10" s="1">
-        <v>0.45175063610076904</v>
+        <v>0.44562524557113647</v>
       </c>
       <c r="D10" s="1">
-        <v>0.45175063610076904</v>
+        <v>0.44562524557113647</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>105600</v>
+        <v>105000</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -20074,19 +18386,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0026189088821411</v>
+        <v>1.0025961399078369</v>
       </c>
       <c r="C11" s="1">
-        <v>0.38897120952606201</v>
+        <v>0.41164901852607727</v>
       </c>
       <c r="D11" s="1">
-        <v>0.38897120952606201</v>
+        <v>0.41164901852607727</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>132600</v>
+        <v>132000</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -20521,25 +18833,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1221</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1222</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1223</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1224</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1225</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1226</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1227</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -20550,10 +18862,10 @@
         <v>1.0078837871551514</v>
       </c>
       <c r="C2" s="1">
-        <v>1.0491085052490234</v>
+        <v>1.0340543985366821</v>
       </c>
       <c r="D2" s="1">
-        <v>1.0491085052490234</v>
+        <v>1.0340543985366821</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -20570,19 +18882,19 @@
         <v>0.98000001907348633</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0083043575286865</v>
+        <v>1.0081506967544556</v>
       </c>
       <c r="C3" s="1">
-        <v>0.74439489841461182</v>
+        <v>0.75732451677322388</v>
       </c>
       <c r="D3" s="1">
-        <v>0.74439489841461182</v>
+        <v>0.75732451677322388</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>41628</v>
+        <v>41400</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -20591,19 +18903,19 @@
         <v>0.99000000953674316</v>
       </c>
       <c r="B4" s="1">
-        <v>1.005638599395752</v>
+        <v>1.0056171417236328</v>
       </c>
       <c r="C4" s="1">
-        <v>0.63436657190322876</v>
+        <v>0.6556122899055481</v>
       </c>
       <c r="D4" s="1">
-        <v>0.63436657190322876</v>
+        <v>0.6556122899055481</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>62334</v>
+        <v>62100</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -20618,7 +18930,7 @@
         <v>0.47426590323448181</v>
       </c>
       <c r="D5" s="1">
-        <v>0.63388442993164063</v>
+        <v>0.63212919235229492</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -20639,7 +18951,7 @@
         <v>0.74246370792388916</v>
       </c>
       <c r="D6" s="1">
-        <v>0.63388442993164063</v>
+        <v>0.63212919235229492</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -20657,10 +18969,10 @@
         <v>1.0044646263122559</v>
       </c>
       <c r="C7" s="1">
-        <v>0.63725286722183228</v>
+        <v>0.62999677658081055</v>
       </c>
       <c r="D7" s="1">
-        <v>0.63388442993164063</v>
+        <v>0.62999677658081055</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -20675,19 +18987,19 @@
         <v>0.99400001764297485</v>
       </c>
       <c r="B8" s="1">
-        <v>1.004095196723938</v>
+        <v>1.0040878057479858</v>
       </c>
       <c r="C8" s="1">
-        <v>0.38480439782142639</v>
+        <v>0.39206090569496155</v>
       </c>
       <c r="D8" s="1">
-        <v>0.58875417709350586</v>
+        <v>0.58314961194992065</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>86388</v>
+        <v>85800</v>
       </c>
       <c r="G8" s="1"/>
     </row>
@@ -20699,10 +19011,10 @@
         <v>1.0034728050231934</v>
       </c>
       <c r="C9" s="1">
-        <v>0.70413613319396973</v>
+        <v>0.69532716274261475</v>
       </c>
       <c r="D9" s="1">
-        <v>0.58875417709350586</v>
+        <v>0.58314961194992065</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -20717,19 +19029,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0031721591949463</v>
+        <v>1.0031633377075195</v>
       </c>
       <c r="C10" s="1">
-        <v>0.4524160623550415</v>
+        <v>0.44866284728050232</v>
       </c>
       <c r="D10" s="1">
-        <v>0.4524160623550415</v>
+        <v>0.44866284728050232</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>116400</v>
+        <v>115320</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -20738,19 +19050,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B11" s="1">
-        <v>1.002619743347168</v>
+        <v>1.0026072263717651</v>
       </c>
       <c r="C11" s="1">
-        <v>0.38804933428764343</v>
+        <v>0.40061074495315552</v>
       </c>
       <c r="D11" s="1">
-        <v>0.38804933428764343</v>
+        <v>0.40061074495315552</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>144000</v>
+        <v>140700</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -22059,25 +20371,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1228</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1229</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1230</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1231</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1232</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1233</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1234</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -22085,19 +20397,19 @@
         <v>0.97000002861022949</v>
       </c>
       <c r="B2" s="1">
-        <v>1.009810209274292</v>
+        <v>1.0094958543777466</v>
       </c>
       <c r="C2" s="1">
-        <v>0.76639515161514282</v>
+        <v>0.79688864946365356</v>
       </c>
       <c r="D2" s="1">
-        <v>0.80508232116699219</v>
+        <v>0.81497126817703247</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>32100</v>
+        <v>31800</v>
       </c>
       <c r="G2" s="1">
         <v>0.97000002861022949</v>
@@ -22111,10 +20423,10 @@
         <v>1.0073263645172119</v>
       </c>
       <c r="C3" s="1">
-        <v>0.83965456485748291</v>
+        <v>0.8319513201713562</v>
       </c>
       <c r="D3" s="1">
-        <v>0.80508232116699219</v>
+        <v>0.81497126817703247</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -22129,19 +20441,19 @@
         <v>0.99000000953674316</v>
       </c>
       <c r="B4" s="1">
-        <v>1.005632758140564</v>
+        <v>1.0055547952651978</v>
       </c>
       <c r="C4" s="1">
-        <v>0.65070706605911255</v>
+        <v>0.69629973173141479</v>
       </c>
       <c r="D4" s="1">
-        <v>0.65070706605911255</v>
+        <v>0.69629973173141479</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>65100</v>
+        <v>64800</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -22150,19 +20462,19 @@
         <v>0.99099999666213989</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0052745342254639</v>
+        <v>1.0052428245544434</v>
       </c>
       <c r="C5" s="1">
-        <v>0.60529845952987671</v>
+        <v>0.63673925399780273</v>
       </c>
       <c r="D5" s="1">
-        <v>0.62496179342269897</v>
+        <v>0.63673925399780273</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>70200</v>
+        <v>69600</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -22174,10 +20486,10 @@
         <v>1.0048713684082031</v>
       </c>
       <c r="C6" s="1">
-        <v>0.6425439715385437</v>
+        <v>0.60248643159866333</v>
       </c>
       <c r="D6" s="1">
-        <v>0.62496179342269897</v>
+        <v>0.6115071177482605</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -22192,19 +20504,19 @@
         <v>0.99299997091293335</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0045064687728882</v>
+        <v>1.00446617603302</v>
       </c>
       <c r="C7" s="1">
-        <v>0.4338289201259613</v>
+        <v>0.47388407588005066</v>
       </c>
       <c r="D7" s="1">
-        <v>0.61175620555877686</v>
+        <v>0.6115071177482605</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>81600</v>
+        <v>81000</v>
       </c>
       <c r="G7" s="1"/>
     </row>
@@ -22216,10 +20528,10 @@
         <v>1.0039323568344116</v>
       </c>
       <c r="C8" s="1">
-        <v>0.71568316221237183</v>
+        <v>0.70820373296737671</v>
       </c>
       <c r="D8" s="1">
-        <v>0.61175620555877686</v>
+        <v>0.6115071177482605</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -22234,19 +20546,19 @@
         <v>0.99500000476837158</v>
       </c>
       <c r="B9" s="1">
-        <v>1.0036426782608032</v>
+        <v>1.003635048866272</v>
       </c>
       <c r="C9" s="1">
-        <v>0.5346565842628479</v>
+        <v>0.34793981909751892</v>
       </c>
       <c r="D9" s="1">
-        <v>0.5346565842628479</v>
+        <v>0.53191715478897095</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>104400</v>
+        <v>104040</v>
       </c>
       <c r="G9" s="1"/>
     </row>
@@ -22255,19 +20567,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0031718015670776</v>
+        <v>1.0029767751693726</v>
       </c>
       <c r="C10" s="1">
-        <v>0.44089263677597046</v>
+        <v>0.63508880138397217</v>
       </c>
       <c r="D10" s="1">
-        <v>0.44089263677597046</v>
+        <v>0.53191715478897095</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>121080</v>
+        <v>120000</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -22723,25 +21035,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1235</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1236</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1237</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1238</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1239</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1240</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1241</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -22749,19 +21061,19 @@
         <v>0.97000002861022949</v>
       </c>
       <c r="B2" s="1">
-        <v>1.015134334564209</v>
+        <v>1.0150810480117798</v>
       </c>
       <c r="C2" s="1">
-        <v>0.68008995056152344</v>
+        <v>0.68524867296218872</v>
       </c>
       <c r="D2" s="1">
-        <v>0.68008995056152344</v>
+        <v>0.68524867296218872</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>41880</v>
+        <v>41448</v>
       </c>
       <c r="G2" s="1">
         <v>0.97000002861022949</v>
@@ -22775,10 +21087,10 @@
         <v>1.0117155313491821</v>
       </c>
       <c r="C3" s="1">
-        <v>0.54372507333755493</v>
+        <v>0.54266124963760376</v>
       </c>
       <c r="D3" s="1">
-        <v>0.54372507333755493</v>
+        <v>0.54266124963760376</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -22793,19 +21105,19 @@
         <v>0.99000000953674316</v>
       </c>
       <c r="B4" s="1">
-        <v>1.0069882869720459</v>
+        <v>1.0069775581359863</v>
       </c>
       <c r="C4" s="1">
-        <v>0.45589834451675415</v>
+        <v>0.46653670072555542</v>
       </c>
       <c r="D4" s="1">
-        <v>0.45589834451675415</v>
+        <v>0.46653670072555542</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>87360</v>
+        <v>87300</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -22901,10 +21213,10 @@
         <v>1.0041029453277588</v>
       </c>
       <c r="C9" s="1">
-        <v>0.3722718358039856</v>
+        <v>0.36558181047439575</v>
       </c>
       <c r="D9" s="1">
-        <v>0.3722718358039856</v>
+        <v>0.36558181047439575</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -22919,19 +21231,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0034685134887695</v>
+        <v>1.0034618377685547</v>
       </c>
       <c r="C10" s="1">
-        <v>0.30015453696250916</v>
+        <v>0.28314125537872314</v>
       </c>
       <c r="D10" s="1">
-        <v>0.30015453696250916</v>
+        <v>0.28314125537872314</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>156000</v>
+        <v>154800</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -22940,19 +21252,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0027631521224976</v>
+        <v>1.0027393102645874</v>
       </c>
       <c r="C11" s="1">
-        <v>0.24520523846149445</v>
+        <v>0.26890715956687927</v>
       </c>
       <c r="D11" s="1">
-        <v>0.24520523846149445</v>
+        <v>0.26890715956687927</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>192540</v>
+        <v>192000</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -23862,25 +22174,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1249</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1250</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1251</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1252</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1253</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1254</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1255</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -24337,25 +22649,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1256</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1257</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1258</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1259</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1260</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1261</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1262</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -24812,25 +23124,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>872</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>873</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>874</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>875</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>876</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>877</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>878</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -25287,25 +23599,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1263</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1264</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1265</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1266</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1267</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1268</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1269</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -25762,25 +24074,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1270</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1271</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1272</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1273</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1274</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1275</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1276</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -26237,25 +24549,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1277</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1278</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1279</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1280</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1281</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1282</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1283</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -26712,25 +25024,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1284</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1285</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1286</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1287</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1288</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1289</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1290</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -28061,25 +26373,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1326</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1327</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1328</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1329</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1330</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1331</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1332</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -28599,25 +26911,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1333</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1334</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1335</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1336</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1337</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1338</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1339</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -29137,25 +27449,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1340</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1341</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1342</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1343</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1344</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1345</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1346</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -29166,10 +27478,10 @@
         <v>1.0044786930084229</v>
       </c>
       <c r="C2" s="1">
-        <v>0.36741563677787781</v>
+        <v>0.34033873677253723</v>
       </c>
       <c r="D2" s="1">
-        <v>0.38905739784240723</v>
+        <v>0.3751789927482605</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -29186,19 +27498,19 @@
         <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0038384199142456</v>
+        <v>1.003811240196228</v>
       </c>
       <c r="C3" s="1">
-        <v>0.41069912910461426</v>
+        <v>0.40733921527862549</v>
       </c>
       <c r="D3" s="1">
-        <v>0.38905739784240723</v>
+        <v>0.3751789927482605</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>54601800</v>
+        <v>53805408</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -29207,19 +27519,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B4" s="1">
-        <v>1.0032429695129395</v>
+        <v>1.0032124519348145</v>
       </c>
       <c r="C4" s="1">
-        <v>0.30417034029960632</v>
+        <v>0.33460712432861328</v>
       </c>
       <c r="D4" s="1">
-        <v>0.30417034029960632</v>
+        <v>0.33460712432861328</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>64700000</v>
+        <v>64680000</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -29675,25 +27987,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1347</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1348</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1349</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1350</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1351</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1352</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1353</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -30213,25 +28525,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1354</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1355</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1356</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1357</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1358</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1359</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1360</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -30242,10 +28554,10 @@
         <v>1.0045175552368164</v>
       </c>
       <c r="C2" s="1">
-        <v>0.38308486342430115</v>
+        <v>0.35965046286582947</v>
       </c>
       <c r="D2" s="1">
-        <v>0.38308486342430115</v>
+        <v>0.37468820810317993</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -30262,19 +28574,19 @@
         <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0038930177688599</v>
+        <v>1.0038695335388184</v>
       </c>
       <c r="C3" s="1">
-        <v>0.2424783855676651</v>
+        <v>0.26591280102729797</v>
       </c>
       <c r="D3" s="1">
-        <v>0.37944382429122925</v>
+        <v>0.37468820810317993</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>55949220</v>
+        <v>55410240</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -30289,7 +28601,7 @@
         <v>0.45319443941116333</v>
       </c>
       <c r="D4" s="1">
-        <v>0.37944382429122925</v>
+        <v>0.37468820810317993</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -30751,25 +29063,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1367</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -32715,6 +31027,544 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>0.99400001764297485</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1.0044879913330078</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.34236431121826172</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.36490613222122192</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>48600000</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.99400001764297485</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>0.99500000476837158</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1.0038225650787354</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.39245721697807312</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.36490613222122192</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>54995580</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>0.99599999189376831</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1.0032087564468384</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.33652642369270325</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.33652642369270325</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>60000000</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>0.99699997901916504</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1.0025399923324585</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.17738611996173859</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.24680998921394348</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>73597712</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>0.99800002574920654</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1.0017131567001343</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.29019990563392639</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.24680998921394348</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>89700000</v>
+      </c>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>0.99900001287460327</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1.0010010004043579</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>720000000</v>
+      </c>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>0.99910002946853638</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1.0009007453918457</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>768000000</v>
+      </c>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>0.99919998645782471</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1.000800609588623</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>816000000</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>0.99930000305175781</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1.0007004737854004</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>864000000</v>
+      </c>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>0.99940001964569092</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1.0006003379821777</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>912000000</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>0.99949997663497925</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1.0005003213882446</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>960000000</v>
+      </c>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>0.99959999322891235</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1.000400185585022</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1008000000</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>0.99970000982284546</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1.0003000497817993</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1056000000</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>0.99980002641677856</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1.0002000331878662</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1104000000</v>
+      </c>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>0.99989998340606689</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1.0001000165939331</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1152000000</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>0.99990999698638916</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1.0000900030136108</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1200000000</v>
+      </c>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>0.99992001056671143</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1.0000799894332886</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1248000000</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>0.99993002414703369</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1.0000699758529663</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1296000000</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>0.99993997812271118</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1.0000600814819336</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1344000000</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>0.99994999170303345</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1.0000500679016113</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1392000000</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1">
+        <v>0.99996000528335571</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1.0000400543212891</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1440000000</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1">
+        <v>0.99997001886367798</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1.0000300407409668</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1488000000</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1">
+        <v>0.99997997283935547</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1.0000200271606445</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1536000000</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1">
+        <v>0.99998998641967773</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1.0000100135803223</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1584000000</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G40"/>

--- a/output/bfm_summary/bfm_norep_pre/merging_points.xlsx
+++ b/output/bfm_summary/bfm_norep_pre/merging_points.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="1377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="1377">
   <si>
     <t>p</t>
   </si>
@@ -14125,7 +14125,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14153,264 +14153,264 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>0.95999997854232788</v>
+        <v>0.99699997901916504</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1.0026073455810547</v>
       </c>
       <c r="C2" s="1">
-        <v>90.490547180175781</v>
+        <v>0.19595378637313843</v>
       </c>
       <c r="D2" s="1">
-        <v>90.490547180175781</v>
+        <v>0.20023404061794281</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>65199200</v>
       </c>
       <c r="G2" s="1">
-        <v>0.99599999189376831</v>
+        <v>0.99699997901916504</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>0.97000002861022949</v>
+        <v>0.99800002574920654</v>
       </c>
       <c r="B3" s="1">
-        <v>0.93289691209793091</v>
+        <v>1.0017991065979004</v>
       </c>
       <c r="C3" s="1">
-        <v>5.9144248962402344</v>
+        <v>0.20451429486274719</v>
       </c>
       <c r="D3" s="1">
-        <v>5.9144248962402344</v>
+        <v>0.20023404061794281</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>611233</v>
+        <v>79024160</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>0.98000001907348633</v>
+        <v>0.99900001287460327</v>
       </c>
       <c r="B4" s="1">
-        <v>0.98372870683670044</v>
+        <v>1.0010010004043579</v>
       </c>
       <c r="C4" s="1">
-        <v>2.7305982112884521</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>2.7305982112884521</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>3590400</v>
+        <v>161331984</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>0.99000000953674316</v>
+        <v>0.99910002946853638</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0013738870620728</v>
+        <v>1.0009007453918457</v>
       </c>
       <c r="C5" s="1">
-        <v>0.82107186317443848</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>1.35292649269104</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>10000000</v>
+        <v>172087456</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>0.99099999666213989</v>
+        <v>0.99919998645782471</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0011919736862183</v>
+        <v>1.000800609588623</v>
       </c>
       <c r="C6" s="1">
-        <v>1.8847812414169312</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>1.35292649269104</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>11516100</v>
+        <v>182842912</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>0.99199998378753662</v>
+        <v>0.99930000305175781</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0020827054977417</v>
+        <v>1.0007004737854004</v>
       </c>
       <c r="C7" s="1">
-        <v>0.936301589012146</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>1.1287733316421509</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>13300390</v>
+        <v>193598384</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>0.99299997091293335</v>
+        <v>0.99940001964569092</v>
       </c>
       <c r="B8" s="1">
-        <v>1.0020164251327515</v>
+        <v>1.0006003379821777</v>
       </c>
       <c r="C8" s="1">
-        <v>1.2834447622299194</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>1.1287733316421509</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>15626079</v>
+        <v>204353856</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>0.99400001764297485</v>
+        <v>0.99949997663497925</v>
       </c>
       <c r="B9" s="1">
-        <v>1.0022995471954346</v>
+        <v>1.0005003213882446</v>
       </c>
       <c r="C9" s="1">
-        <v>0.94025421142578125</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>1.1287733316421509</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>18714120</v>
+        <v>215109312</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>0.99500000476837158</v>
+        <v>0.99959999322891235</v>
       </c>
       <c r="B10" s="1">
-        <v>1.0022372007369995</v>
+        <v>1.000400185585022</v>
       </c>
       <c r="C10" s="1">
-        <v>1.355083703994751</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>1.1287733316421509</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>22997670</v>
+        <v>225864784</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>0.99599999189376831</v>
+        <v>0.99970000982284546</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0025913715362549</v>
+        <v>1.0003000497817993</v>
       </c>
       <c r="C11" s="1">
-        <v>0.73612093925476074</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>0.73612093925476074</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>29246016</v>
+        <v>236620256</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>0.99699997901916504</v>
+        <v>0.99980002641677856</v>
       </c>
       <c r="B12" s="1">
-        <v>1.002324104309082</v>
+        <v>1.0002000331878662</v>
       </c>
       <c r="C12" s="1">
-        <v>0.37784230709075928</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>0.37784230709075928</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>39437200</v>
+        <v>247375712</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>0.99800002574920654</v>
+        <v>0.99989998340606689</v>
       </c>
       <c r="B13" s="1">
-        <v>1.00169837474823</v>
+        <v>1.0001000165939331</v>
       </c>
       <c r="C13" s="1">
-        <v>0.30495834350585938</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>0.30495834350585938</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>57729656</v>
+        <v>258131168</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>0.99900001287460327</v>
+        <v>0.99990999698638916</v>
       </c>
       <c r="B14" s="1">
-        <v>1.0010010004043579</v>
+        <v>1.0000900030136108</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
@@ -14422,16 +14422,16 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>102440072</v>
+        <v>268886656</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>0.99910002946853638</v>
+        <v>0.99992001056671143</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0009007453918457</v>
+        <v>1.0000799894332886</v>
       </c>
       <c r="C15" s="1">
         <v>0</v>
@@ -14443,16 +14443,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>111023768</v>
+        <v>279642112</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>0.99919998645782471</v>
+        <v>0.99993002414703369</v>
       </c>
       <c r="B16" s="1">
-        <v>1.000800609588623</v>
+        <v>1.0000699758529663</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
@@ -14464,16 +14464,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>121077512</v>
+        <v>290397568</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>0.99930000305175781</v>
+        <v>0.99993997812271118</v>
       </c>
       <c r="B17" s="1">
-        <v>1.0007004737854004</v>
+        <v>1.0000600814819336</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -14485,16 +14485,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>133104824</v>
+        <v>301153024</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>0.99940001964569092</v>
+        <v>0.99994999170303345</v>
       </c>
       <c r="B18" s="1">
-        <v>1.0006003379821777</v>
+        <v>1.0000500679016113</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -14506,16 +14506,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>147782672</v>
+        <v>311908512</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>0.99949997663497925</v>
+        <v>0.99996000528335571</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0005003213882446</v>
+        <v>1.0000400543212891</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -14527,16 +14527,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>165757120</v>
+        <v>322663968</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>0.99959999322891235</v>
+        <v>0.99997001886367798</v>
       </c>
       <c r="B20" s="1">
-        <v>1.000400185585022</v>
+        <v>1.0000300407409668</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -14548,16 +14548,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>191315168</v>
+        <v>333419456</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>0.99970000982284546</v>
+        <v>0.99997997283935547</v>
       </c>
       <c r="B21" s="1">
-        <v>1.0003000497817993</v>
+        <v>1.0000200271606445</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -14569,16 +14569,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>230000000</v>
+        <v>344174912</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>0.99980002641677856</v>
+        <v>0.99998998641967773</v>
       </c>
       <c r="B22" s="1">
-        <v>1.0002000331878662</v>
+        <v>1.0000100135803223</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
@@ -14590,219 +14590,9 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>296579616</v>
+        <v>354930368</v>
       </c>
       <c r="G22" s="1"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1">
-        <v>0.99989998340606689</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1.0001000165939331</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>449530304</v>
-      </c>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1">
-        <v>0.99990999698638916</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1.0000900030136108</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
-        <v>478972480</v>
-      </c>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1">
-        <v>0.99992001056671143</v>
-      </c>
-      <c r="B25" s="1">
-        <v>1.0000799894332886</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
-        <v>504058400</v>
-      </c>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>0.99993002414703369</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.0000699758529663</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>541594304</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>0.99993997812271118</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1.0000600814819336</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>586247872</v>
-      </c>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>0.99994999170303345</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1.0000500679016113</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>633138176</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>0.99996000528335571</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.0000400543212891</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>727102272</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1">
-        <v>0.99997001886367798</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1.0000300407409668</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>827948864</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>0.99997997283935547</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1.0000200271606445</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>988932288</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1">
-        <v>0.99998998641967773</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1.0000100135803223</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1406332928</v>
-      </c>
-      <c r="G32" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -14841,19 +14631,19 @@
         <v>0.99500000476837158</v>
       </c>
       <c r="B2" s="1">
-        <v>1.003908634185791</v>
+        <v>1.0039409399032593</v>
       </c>
       <c r="C2" s="1">
-        <v>0.36255764961242676</v>
+        <v>0.42843782901763916</v>
       </c>
       <c r="D2" s="1">
-        <v>0.36255764961242676</v>
+        <v>0.42843782901763916</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>46823200</v>
+        <v>48000000</v>
       </c>
       <c r="G2" s="1">
         <v>0.99500000476837158</v>
@@ -14864,19 +14654,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0032647848129272</v>
+        <v>1.0033631324768066</v>
       </c>
       <c r="C3" s="1">
-        <v>0.27674007415771484</v>
+        <v>0.30686292052268982</v>
       </c>
       <c r="D3" s="1">
-        <v>0.27674007415771484</v>
+        <v>0.30686292052268982</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>60999996</v>
+        <v>61334400</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -14885,19 +14675,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B4" s="1">
-        <v>1.0025360584259033</v>
+        <v>1.0026645660400391</v>
       </c>
       <c r="C4" s="1">
-        <v>0.22319909930229187</v>
+        <v>0.17054145038127899</v>
       </c>
       <c r="D4" s="1">
-        <v>0.24164377152919769</v>
+        <v>0.17190945148468018</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>69200000</v>
+        <v>70779904</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -14906,19 +14696,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0017551183700562</v>
+        <v>1.0018306970596313</v>
       </c>
       <c r="C5" s="1">
-        <v>0.24835091829299927</v>
+        <v>0.17293545603752136</v>
       </c>
       <c r="D5" s="1">
-        <v>0.24164377152919769</v>
+        <v>0.17190945148468018</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>76054656</v>
+        <v>85200000</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -17657,19 +17447,19 @@
         <v>0.99400001764297485</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0044560432434082</v>
+        <v>1.004341721534729</v>
       </c>
       <c r="C2" s="1">
-        <v>0.34276136755943298</v>
+        <v>0.45646980404853821</v>
       </c>
       <c r="D2" s="1">
-        <v>0.39582076668739319</v>
+        <v>0.475749671459198</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>53354504</v>
+        <v>52568704</v>
       </c>
       <c r="G2" s="1">
         <v>0.99400001764297485</v>
@@ -17683,10 +17473,10 @@
         <v>1.0037910938262939</v>
       </c>
       <c r="C3" s="1">
-        <v>0.4382682740688324</v>
+        <v>0.49389541149139404</v>
       </c>
       <c r="D3" s="1">
-        <v>0.39582076668739319</v>
+        <v>0.475749671459198</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -17701,19 +17491,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B4" s="1">
-        <v>1.0032232999801636</v>
+        <v>1.0032792091369629</v>
       </c>
       <c r="C4" s="1">
-        <v>0.32415083050727844</v>
+        <v>0.32721850275993347</v>
       </c>
       <c r="D4" s="1">
-        <v>0.32415083050727844</v>
+        <v>0.32721850275993347</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>71100000</v>
+        <v>72000000</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -17722,19 +17512,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0025421380996704</v>
+        <v>1.0026010274887085</v>
       </c>
       <c r="C5" s="1">
-        <v>0.19366089999675751</v>
+        <v>0.19325190782546997</v>
       </c>
       <c r="D5" s="1">
-        <v>0.23533287644386292</v>
+        <v>0.20416015386581421</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>84768840</v>
+        <v>86400000</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -17743,19 +17533,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0017316341400146</v>
+        <v>1.0017900466918945</v>
       </c>
       <c r="C6" s="1">
-        <v>0.27179586887359619</v>
+        <v>0.21351006627082825</v>
       </c>
       <c r="D6" s="1">
-        <v>0.23533287644386292</v>
+        <v>0.20416015386581421</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>94206600</v>
+        <v>95033600</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -21699,25 +21489,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1242</v>
+        <v>1368</v>
       </c>
       <c r="B1" t="s">
-        <v>1243</v>
+        <v>1369</v>
       </c>
       <c r="C1" t="s">
-        <v>1244</v>
+        <v>1370</v>
       </c>
       <c r="D1" t="s">
-        <v>1245</v>
+        <v>1371</v>
       </c>
       <c r="E1" t="s">
-        <v>1246</v>
+        <v>1372</v>
       </c>
       <c r="F1" t="s">
-        <v>1247</v>
+        <v>1373</v>
       </c>
       <c r="G1" t="s">
-        <v>1248</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2">
@@ -21725,19 +21515,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0025300979614258</v>
+        <v>1.0025498867034912</v>
       </c>
       <c r="C2" s="1">
-        <v>0.22701236605644226</v>
+        <v>0.22333818674087524</v>
       </c>
       <c r="D2" s="1">
-        <v>0.24147605895996094</v>
+        <v>0.22985272109508514</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>13794000</v>
+        <v>14994000</v>
       </c>
       <c r="G2" s="1">
         <v>0.99699997901916504</v>
@@ -21748,19 +21538,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0017529726028442</v>
+        <v>1.0017690658569336</v>
       </c>
       <c r="C3" s="1">
-        <v>0.25051587820053101</v>
+        <v>0.23450595140457153</v>
       </c>
       <c r="D3" s="1">
-        <v>0.24147605895996094</v>
+        <v>0.22985272109508514</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>16428000</v>
+        <v>16729200</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -22675,19 +22465,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0025280714035034</v>
+        <v>1.0026150941848755</v>
       </c>
       <c r="C2" s="1">
-        <v>0.22548498213291168</v>
+        <v>0.17852932214736938</v>
       </c>
       <c r="D2" s="1">
-        <v>0.23979935050010681</v>
+        <v>0.19638863205909729</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>24000000</v>
+        <v>25355604</v>
       </c>
       <c r="G2" s="1">
         <v>0.99699997901916504</v>
@@ -22698,19 +22488,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0017493963241577</v>
+        <v>1.0017893314361572</v>
       </c>
       <c r="C3" s="1">
-        <v>0.25411373376846313</v>
+        <v>0.21424795687198639</v>
       </c>
       <c r="D3" s="1">
-        <v>0.23979935050010681</v>
+        <v>0.19638863205909729</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>30797316</v>
+        <v>31176000</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -23150,19 +22940,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0025128126144409</v>
+        <v>1.0026106834411621</v>
       </c>
       <c r="C2" s="1">
-        <v>0.21259219944477081</v>
+        <v>0.18235582113265991</v>
       </c>
       <c r="D2" s="1">
-        <v>0.25730463862419128</v>
+        <v>0.20132288336753845</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>21600000</v>
+        <v>25186812</v>
       </c>
       <c r="G2" s="1">
         <v>0.99699997901916504</v>
@@ -23173,19 +22963,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0017212629318237</v>
+        <v>1.0017887353897095</v>
       </c>
       <c r="C3" s="1">
-        <v>0.28214487433433533</v>
+        <v>0.21487078070640564</v>
       </c>
       <c r="D3" s="1">
-        <v>0.25730463862419128</v>
+        <v>0.20132288336753845</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>28865400</v>
+        <v>28980000</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -23625,19 +23415,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B2" s="1">
-        <v>1.002534031867981</v>
+        <v>1.0025602579116821</v>
       </c>
       <c r="C2" s="1">
-        <v>0.19613939523696899</v>
+        <v>0.2119867205619812</v>
       </c>
       <c r="D2" s="1">
-        <v>0.24875834584236145</v>
+        <v>0.22761371731758118</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>37411200</v>
+        <v>38400000</v>
       </c>
       <c r="G2" s="1">
         <v>0.99699997901916504</v>
@@ -23648,19 +23438,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0017259120941162</v>
+        <v>1.0017681121826172</v>
       </c>
       <c r="C3" s="1">
-        <v>0.27745959162712097</v>
+        <v>0.23542721569538116</v>
       </c>
       <c r="D3" s="1">
-        <v>0.24875834584236145</v>
+        <v>0.22761371731758118</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>46764000</v>
+        <v>47172000</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -24575,19 +24365,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0025327205657959</v>
+        <v>1.0026094913482666</v>
       </c>
       <c r="C2" s="1">
-        <v>0.16632203757762909</v>
+        <v>0.17668959498405457</v>
       </c>
       <c r="D2" s="1">
-        <v>0.24221351742744446</v>
+        <v>0.19919601082801819</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>52800000</v>
+        <v>68796000</v>
       </c>
       <c r="G2" s="1">
         <v>0.99699997901916504</v>
@@ -24598,19 +24388,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0016946792602539</v>
+        <v>1.0017818212509155</v>
       </c>
       <c r="C3" s="1">
-        <v>0.30861857533454895</v>
+        <v>0.22170241177082062</v>
       </c>
       <c r="D3" s="1">
-        <v>0.24221351742744446</v>
+        <v>0.19919601082801819</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>88454280</v>
+        <v>89148048</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -26399,19 +26189,19 @@
         <v>0.99400001764297485</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0044558048248291</v>
+        <v>1.004320502281189</v>
       </c>
       <c r="C2" s="1">
-        <v>0.36671385169029236</v>
+        <v>0.57695770263671875</v>
       </c>
       <c r="D2" s="1">
-        <v>0.39545130729675293</v>
+        <v>0.57695770263671875</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>48875760</v>
+        <v>48000000</v>
       </c>
       <c r="G2" s="1">
         <v>0.99400001764297485</v>
@@ -26422,19 +26212,19 @@
         <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0038148164749146</v>
+        <v>1.0038909912109375</v>
       </c>
       <c r="C3" s="1">
-        <v>0.4200834333896637</v>
+        <v>0.42756327986717224</v>
       </c>
       <c r="D3" s="1">
-        <v>0.39545130729675293</v>
+        <v>0.42756327986717224</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>52920000</v>
+        <v>53980000</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -26443,19 +26233,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B4" s="1">
-        <v>1.0032287836074829</v>
+        <v>1.003312349319458</v>
       </c>
       <c r="C4" s="1">
-        <v>0.31617444753646851</v>
+        <v>0.29272416234016418</v>
       </c>
       <c r="D4" s="1">
-        <v>0.31617444753646851</v>
+        <v>0.29272416234016418</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>61800000</v>
+        <v>64000000</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -26464,19 +26254,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0025396347045898</v>
+        <v>1.0025995969772339</v>
       </c>
       <c r="C5" s="1">
-        <v>0.20295411348342896</v>
+        <v>0.20335839688777924</v>
       </c>
       <c r="D5" s="1">
-        <v>0.24019880592823029</v>
+        <v>0.20412690937519073</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>82157760</v>
+        <v>83925360</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -26485,19 +26275,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B6" s="1">
-        <v>1.001738429069519</v>
+        <v>1.0017987489700317</v>
       </c>
       <c r="C6" s="1">
-        <v>0.26502859592437744</v>
+        <v>0.20478563010692596</v>
       </c>
       <c r="D6" s="1">
-        <v>0.24019880592823029</v>
+        <v>0.20412690937519073</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>91366288</v>
+        <v>102697200</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -28013,19 +27803,19 @@
         <v>0.99400001764297485</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0045040845870972</v>
+        <v>1.0044620037078857</v>
       </c>
       <c r="C2" s="1">
-        <v>0.33983266353607178</v>
+        <v>0.58360439538955688</v>
       </c>
       <c r="D2" s="1">
-        <v>0.3902353048324585</v>
+        <v>0.58360439538955688</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>42405600</v>
+        <v>42338560</v>
       </c>
       <c r="G2" s="1">
         <v>0.99400001764297485</v>
@@ -28036,19 +27826,19 @@
         <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0038361549377441</v>
+        <v>1.0040390491485596</v>
       </c>
       <c r="C3" s="1">
-        <v>0.42943733930587769</v>
+        <v>0.34374552965164185</v>
       </c>
       <c r="D3" s="1">
-        <v>0.3902353048324585</v>
+        <v>0.34374552965164185</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>46971280</v>
+        <v>48795540</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -28057,19 +27847,19 @@
         <v>0.99599999189376831</v>
       </c>
       <c r="B4" s="1">
-        <v>1.0032594203948975</v>
+        <v>1.0033761262893677</v>
       </c>
       <c r="C4" s="1">
-        <v>0.31870314478874207</v>
+        <v>0.28642198443412781</v>
       </c>
       <c r="D4" s="1">
-        <v>0.31870314478874207</v>
+        <v>0.28642198443412781</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>54000000</v>
+        <v>54816744</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -28078,19 +27868,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B5" s="1">
-        <v>1.002572774887085</v>
+        <v>1.0026570558547974</v>
       </c>
       <c r="C5" s="1">
-        <v>0.1936754584312439</v>
+        <v>0.10974942892789841</v>
       </c>
       <c r="D5" s="1">
-        <v>0.21961340308189392</v>
+        <v>0.19740204513072968</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>61800000</v>
+        <v>66751160</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -28105,7 +27895,7 @@
         <v>0.24122835695743561</v>
       </c>
       <c r="D6" s="1">
-        <v>0.21961340308189392</v>
+        <v>0.19740204513072968</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -29092,10 +28882,10 @@
         <v>1.0044857263565063</v>
       </c>
       <c r="C2" s="1">
-        <v>0.35792291164398193</v>
+        <v>0.46303638815879822</v>
       </c>
       <c r="D2" s="1">
-        <v>0.38059172034263611</v>
+        <v>0.46303638815879822</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -29112,19 +28902,19 @@
         <v>0.99500000476837158</v>
       </c>
       <c r="B3" s="1">
-        <v>1.003835916519165</v>
+        <v>1.003941535949707</v>
       </c>
       <c r="C3" s="1">
-        <v>0.39628550410270691</v>
+        <v>0.29117202758789062</v>
       </c>
       <c r="D3" s="1">
-        <v>0.38059172034263611</v>
+        <v>0.35059913992881775</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>48999996</v>
+        <v>50248092</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -29136,10 +28926,10 @@
         <v>1.0032259225845337</v>
       </c>
       <c r="C4" s="1">
-        <v>0.34814044833183289</v>
+        <v>0.40012174844741821</v>
       </c>
       <c r="D4" s="1">
-        <v>0.34814044833183289</v>
+        <v>0.35059913992881775</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -29154,19 +28944,19 @@
         <v>0.99699997901916504</v>
       </c>
       <c r="B5" s="1">
-        <v>1.0025688409805298</v>
+        <v>1.0026209354400635</v>
       </c>
       <c r="C5" s="1">
-        <v>0.15094777941703796</v>
+        <v>0.19832274317741394</v>
       </c>
       <c r="D5" s="1">
-        <v>0.23899570107460022</v>
+        <v>0.19832274317741394</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>66000000</v>
+        <v>66976596</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -29175,19 +28965,19 @@
         <v>0.99800002574920654</v>
       </c>
       <c r="B6" s="1">
-        <v>1.0017155408859253</v>
+        <v>1.0018150806427002</v>
       </c>
       <c r="C6" s="1">
-        <v>0.28791120648384094</v>
+        <v>0.18855209648609161</v>
       </c>
       <c r="D6" s="1">
-        <v>0.23899570107460022</v>
+        <v>0.18855209648609161</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>84000000</v>
+        <v>115781040</v>
       </c>
       <c r="G6" s="1"/>
     </row>
